--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,221 +425,291 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A32"/>
+  <dimension ref="A2:A42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>zuzbQnCF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>lONsG15D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>tvOIPExA</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
+        <is>
+          <t>W67CmLPh</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A42"/>
+  <dimension ref="A2:A33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -438,278 +438,215 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>lONsG15D</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>t0w6KHuf</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>AuVMGZvJ</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>KSwfVwAO</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>pzHxyrtm</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>dCPKovw8</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>vXAKoaf5</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A33"/>
+  <dimension ref="A2:A41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -438,215 +438,271 @@
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>GbeXvnR8</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>O48oHrZ1</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>dfO6OQtS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>SxFxJ44k</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>AuVMGZvJ</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>pWQQJq6l</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>hIsO3XFj</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>EF8gXauC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>lONsG15D</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>0K2qBFNG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>Kj4sifWp</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
+          <t>bF2q76Mr</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>6q2yrHgU</t>
+          <t>vyk5gjdE</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>AiJ3kset</t>
+          <t>tbKZHNz1</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>YV3TqwPH</t>
+          <t>MZjh9ghT</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>l0ueP5rR</t>
+          <t>f1nnRRDE</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>t2AoZLAa</t>
+          <t>8QPARz8c</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>jFMCm08e</t>
+          <t>hzyf0b9b</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>tvOIPExA</t>
+          <t>CpiTEcOi</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>KSwfVwAO</t>
+          <t>8CpxDyg4</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>pzHxyrtm</t>
+          <t>6q2yrHgU</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>dCPKovw8</t>
+          <t>AiJ3kset</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>vXAKoaf5</t>
+          <t>YV3TqwPH</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>06NAdG8N</t>
+          <t>l0ueP5rR</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>Sff03OL7</t>
+          <t>t2AoZLAa</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>EkP2bxvB</t>
+          <t>jFMCm08e</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>pAXo2Kvn</t>
+          <t>tvOIPExA</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>KSwfVwAO</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
+          <t>pzHxyrtm</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="1" t="inlineStr">
+        <is>
+          <t>dCPKovw8</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="1" t="inlineStr">
+        <is>
+          <t>vXAKoaf5</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="1" t="inlineStr">
+        <is>
+          <t>06NAdG8N</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="1" t="inlineStr">
+        <is>
+          <t>Sff03OL7</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="1" t="inlineStr">
+        <is>
+          <t>EkP2bxvB</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="1" t="inlineStr">
+        <is>
+          <t>pAXo2Kvn</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="1" t="inlineStr">
         <is>
           <t>fcxqFy2l</t>
         </is>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A41"/>
+  <dimension ref="A2:A25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -494,217 +494,105 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>06NAdG8N</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
+          <t>Sff03OL7</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>8QPARz8c</t>
+          <t>EkP2bxvB</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hzyf0b9b</t>
+          <t>pAXo2Kvn</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>CpiTEcOi</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>8CpxDyg4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A41"/>
+  <dimension ref="A2:A21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -494,217 +494,77 @@
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pWQQJq6l</t>
+          <t>djSMofvg</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hIsO3XFj</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>EF8gXauC</t>
+          <t>AgAeVYgC</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>lONsG15D</t>
+          <t>QVJwrCwI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>0K2qBFNG</t>
+          <t>61DvZGfm</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>Kj4sifWp</t>
+          <t>0OYDmG9t</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>bF2q76Mr</t>
+          <t>AVR8vwXP</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>vyk5gjdE</t>
+          <t>W8b4TCOO</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>tbKZHNz1</t>
+          <t>2T6mXfPa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>MZjh9ghT</t>
+          <t>W67CmLPh</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>f1nnRRDE</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="1" t="inlineStr">
-        <is>
-          <t>8QPARz8c</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="1" t="inlineStr">
-        <is>
-          <t>hzyf0b9b</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="1" t="inlineStr">
-        <is>
-          <t>CpiTEcOi</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="1" t="inlineStr">
-        <is>
-          <t>8CpxDyg4</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="1" t="inlineStr">
-        <is>
-          <t>6q2yrHgU</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="1" t="inlineStr">
-        <is>
-          <t>AiJ3kset</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="1" t="inlineStr">
-        <is>
-          <t>YV3TqwPH</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="1" t="inlineStr">
-        <is>
-          <t>l0ueP5rR</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="1" t="inlineStr">
-        <is>
-          <t>t2AoZLAa</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="1" t="inlineStr">
-        <is>
-          <t>jFMCm08e</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="1" t="inlineStr">
-        <is>
-          <t>tvOIPExA</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="1" t="inlineStr">
-        <is>
-          <t>KSwfVwAO</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="1" t="inlineStr">
-        <is>
-          <t>pzHxyrtm</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="1" t="inlineStr">
-        <is>
-          <t>dCPKovw8</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="1" t="inlineStr">
-        <is>
-          <t>vXAKoaf5</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="1" t="inlineStr">
-        <is>
-          <t>06NAdG8N</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="1" t="inlineStr">
-        <is>
-          <t>Sff03OL7</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="1" t="inlineStr">
-        <is>
-          <t>EkP2bxvB</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="1" t="inlineStr">
-        <is>
-          <t>pAXo2Kvn</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="1" t="inlineStr">
-        <is>
-          <t>fcxqFy2l</t>
+          <t>6u6i5pie</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,77 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A21"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>zuzbQnCF</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ltDOVSGt</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>borges sanches yvandro</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>zZ9n9OAn</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>hack robin</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +503,12 @@
           <t>YZZcMwBs</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +516,12 @@
           <t>GbeXvnR8</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +529,12 @@
           <t>O48oHrZ1</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +542,12 @@
           <t>2FREIeA6</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +555,12 @@
           <t>dfO6OQtS</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +568,12 @@
           <t>SxFxJ44k</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +581,12 @@
           <t>t0w6KHuf</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +594,12 @@
           <t>AuVMGZvJ</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +607,12 @@
           <t>djSMofvg</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +620,12 @@
           <t>U3QUqY85</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +633,12 @@
           <t>AgAeVYgC</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +646,12 @@
           <t>QVJwrCwI</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +659,12 @@
           <t>61DvZGfm</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -532,6 +672,12 @@
           <t>0OYDmG9t</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -539,6 +685,12 @@
           <t>AVR8vwXP</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -546,6 +698,12 @@
           <t>W8b4TCOO</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -553,20 +711,12 @@
           <t>2T6mXfPa</t>
         </is>
       </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="1" t="inlineStr">
-        <is>
-          <t>W67CmLPh</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="1" t="inlineStr">
-        <is>
-          <t>6u6i5pie</t>
-        </is>
-      </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G19"/>
+  <dimension ref="A1:AC7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -459,74 +459,450 @@
           <t>player_name_miss_home_3</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zuzbQnCF</t>
+          <t>YZZcMwBs</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ltDOVSGt</t>
+          <t>bi35uzgT</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>borges sanches yvandro</t>
+          <t>dahmen finn</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>zZ9n9OAn</t>
+          <t>OKcwlyhN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>hack robin</t>
+          <t>framberger raphael</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ruMn6c8t</t>
+          <t>x8uj789H</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>walde simon</t>
-        </is>
-      </c>
+          <t>gumny robert</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>4MB78NvI</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>keita naby</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4pESGQSm</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>pieper amos</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>GbeXvnR8</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>UwlvfZCm</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>atubolu noah</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bLZ4JBQc</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>gulde manuel</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>ja18uZOO</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>nartey nikolas</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>IkPmFRac</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>pfeiffer luca</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>b7FJ7Yb9</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>WCM2C2l0</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>sildillia kiliann</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>YFNUTMWH</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>raimund luca</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>hCWLxEzr</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>rouault anthony</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>vVKqrtep</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>stergiou leonidas</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>MNTqORR3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>vagnoman josha</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>O48oHrZ1</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tbJx15yJ</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bebou ihlas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>OrIOjLpG</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>KWrYlSTD</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>berisha mergim</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>4lxZ6TzS</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>johansson carl</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>fRZB21nI</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bischof tom</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>AF2Br9IA</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>jurasek david</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>EkcE3L0c</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>skrzybski steven</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>QaQIZA1a</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>nsoki stanley</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
+          <t>2FREIeA6</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -535,188 +911,226 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>fVThrU8C</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>roussillon jerome</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>Oh6gIVja</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>stein yannic</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>dnpDxpQf</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>volland kevin</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr"/>
-      <c r="G6" t="inlineStr"/>
+          <t>dfO6OQtS</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>6DL0LD7a</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bitshiabu el chadaille</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>vDVD8EAA</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>elmas elif</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>bs71GRSt</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>ouedraogo assan</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>MwxzFrgA</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>bernardo</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>40wafXg4</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>ordets ivan</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>dGcprQ0r</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>riemann manuel</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>4bt7xopA</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>tolba mohammed</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+          <t>SxFxJ44k</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>YXRCmup6</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>guirassy serhou</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Umh5qbVs</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>watjen kjell</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>SxFxJ44k</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr"/>
-      <c r="G8" t="inlineStr"/>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>t0w6KHuf</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
-          <t>AuVMGZvJ</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr"/>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr"/>
-      <c r="G10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>djSMofvg</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr"/>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr"/>
-      <c r="G11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>U3QUqY85</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr"/>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr"/>
-      <c r="G12" t="inlineStr"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr"/>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr"/>
-      <c r="G13" t="inlineStr"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr"/>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr"/>
-      <c r="G14" t="inlineStr"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr"/>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr"/>
-      <c r="G15" t="inlineStr"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr"/>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr"/>
-      <c r="G16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr"/>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr"/>
-      <c r="G17" t="inlineStr"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr"/>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr"/>
-      <c r="G18" t="inlineStr"/>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr"/>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr"/>
-      <c r="G19" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>pYy1apYK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>wenig marcel</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AC7"/>
+  <dimension ref="A1:W12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,448 +461,272 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_home_6</t>
+          <t>id_player_miss_away_3</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_home_6</t>
+          <t>player_name_miss_away_3</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_3</t>
+          <t>id_player_miss_away_4</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_3</t>
+          <t>player_name_miss_away_4</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_4</t>
+          <t>id_player_miss_away_5</t>
         </is>
       </c>
       <c r="U1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_4</t>
+          <t>player_name_miss_away_5</t>
         </is>
       </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
-          <t>id_player_miss_away_5</t>
+          <t>id_player_miss_away_6</t>
         </is>
       </c>
       <c r="W1" s="1" t="inlineStr">
         <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
           <t>player_name_miss_away_6</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_7</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>YZZcMwBs</t>
+          <t>t0w6KHuf</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>bi35uzgT</t>
+          <t>lla8DJW0</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>dahmen finn</t>
+          <t>amoura mohamed</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>OKcwlyhN</t>
+          <t>6D2Vm8M8</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>framberger raphael</t>
+          <t>nmecha lukas</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>x8uj789H</t>
+          <t>ddHjOAgc</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>gumny robert</t>
+          <t>odogu david</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4MB78NvI</t>
+          <t>lIg2Sr9i</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>keita naby</t>
+          <t>paredes kevin</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4pESGQSm</t>
+          <t>OrlbhXJo</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>pieper amos</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>fw8tPLtH</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>ibrahimovic arijon</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>MVgAbUb4</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>daniel peretz</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>GlTyfr8U</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>sane leroy</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>GbeXvnR8</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>UwlvfZCm</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>atubolu noah</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>tprC8Q14</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>ezekwem kimberly</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>bLZ4JBQc</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>gulde manuel</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>ja18uZOO</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>nartey nikolas</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>IkPmFRac</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>pfeiffer luca</t>
-        </is>
-      </c>
+          <t>AuVMGZvJ</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>tUPHhVGD</t>
+          <t>vTDGEfNG</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>kyereh daniel kofi</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>b7FJ7Yb9</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>rohl merlin</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>WCM2C2l0</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>sildillia kiliann</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>YFNUTMWH</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>raimund luca</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>hCWLxEzr</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>rouault anthony</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>vVKqrtep</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>stergiou leonidas</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>MNTqORR3</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>vagnoman josha</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>j1IjJkHI</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>zagadou dan axel</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
+          <t>keller thomas</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>O48oHrZ1</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>tbJx15yJ</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>bebou ihlas</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>OrIOjLpG</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>becker finn ole</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>KWrYlSTD</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>berisha mergim</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>4lxZ6TzS</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>johansson carl</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>O4aDKvnH</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>kleine bekel colin noah</t>
-        </is>
-      </c>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>fRZB21nI</t>
-        </is>
-      </c>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>bischof tom</t>
-        </is>
-      </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>AF2Br9IA</t>
-        </is>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>jurasek david</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>nBbGuPN8</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>kabak ozan</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr">
-        <is>
-          <t>EkcE3L0c</t>
-        </is>
-      </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>skrzybski steven</t>
-        </is>
-      </c>
+          <t>djSMofvg</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
       <c r="T4" t="inlineStr"/>
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>QaQIZA1a</t>
-        </is>
-      </c>
-      <c r="AC4" t="inlineStr">
-        <is>
-          <t>nsoki stanley</t>
-        </is>
-      </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>2FREIeA6</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B5" t="inlineStr"/>
@@ -911,208 +735,68 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>WznPyl4k</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>juranovic josip</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>fVThrU8C</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>roussillon jerome</t>
-        </is>
-      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr"/>
       <c r="Q5" t="inlineStr"/>
-      <c r="R5" t="inlineStr">
-        <is>
-          <t>Oh6gIVja</t>
-        </is>
-      </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>stein yannic</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>dnpDxpQf</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>volland kevin</t>
-        </is>
-      </c>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>dfO6OQtS</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>6DL0LD7a</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>bitshiabu el chadaille</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>vDVD8EAA</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>elmas elif</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>bs71GRSt</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>ouedraogo assan</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>MwxzFrgA</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>bernardo</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>40wafXg4</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>ordets ivan</t>
-        </is>
-      </c>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>M1bcCLIU</t>
-        </is>
-      </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>schlager xaver</t>
-        </is>
-      </c>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr"/>
       <c r="Q6" t="inlineStr"/>
-      <c r="R6" t="inlineStr">
-        <is>
-          <t>dGcprQ0r</t>
-        </is>
-      </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>riemann manuel</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>4bt7xopA</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>tolba mohammed</t>
-        </is>
-      </c>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>SxFxJ44k</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>YXRCmup6</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>guirassy serhou</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>Umh5qbVs</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>watjen kjell</t>
-        </is>
-      </c>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>4MlIIRDU</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>loune mehdi</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>pYy1apYK</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>wenig marcel</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
@@ -1125,12 +809,151 @@
       <c r="U7" t="inlineStr"/>
       <c r="V7" t="inlineStr"/>
       <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,157 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>djSMofvg</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>fVThrU8C</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>roussillon jerome</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Oh6gIVja</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>stein yannic</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>dnpDxpQf</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>volland kevin</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>QwxAZ5yD</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>burchert sascha</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>rD3WL6oI</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>zoller simon</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +583,20 @@
           <t>U3QUqY85</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +604,20 @@
           <t>AgAeVYgC</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +625,20 @@
           <t>QVJwrCwI</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +646,20 @@
           <t>61DvZGfm</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +667,20 @@
           <t>0OYDmG9t</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +688,20 @@
           <t>AVR8vwXP</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +709,20 @@
           <t>W8b4TCOO</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +730,20 @@
           <t>2T6mXfPa</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O10"/>
+  <dimension ref="A1:AA16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -499,235 +499,791 @@
           <t>player_name_miss_away_3</t>
         </is>
       </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>djSMofvg</t>
+          <t>U3QUqY85</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>WznPyl4k</t>
+          <t>MwxzFrgA</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>juranovic josip</t>
+          <t>bernardo</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>fVThrU8C</t>
+          <t>40wafXg4</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>roussillon jerome</t>
+          <t>ordets ivan</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Oh6gIVja</t>
+          <t>dGcprQ0r</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>stein yannic</t>
+          <t>riemann manuel</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>dnpDxpQf</t>
+          <t>4bt7xopA</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>volland kevin</t>
+          <t>tolba mohammed</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>6y5I2kuT</t>
+          <t>ltDOVSGt</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>ahlers soren</t>
+          <t>borges sanches yvandro</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>QwxAZ5yD</t>
+          <t>MyyplBl4</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>burchert sascha</t>
+          <t>olschowsky jan</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>rD3WL6oI</t>
+          <t>ruMn6c8t</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>zoller simon</t>
-        </is>
-      </c>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>U3QUqY85</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr"/>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
+          <t>AgAeVYgC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>pYy1apYK</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>wenig marcel</t>
+        </is>
+      </c>
       <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>tbJx15yJ</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>bebou ihlas</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>OrIOjLpG</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>fRZB21nI</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>bischof tom</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>AF2Br9IA</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>jurasek david</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>AgAeVYgC</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr"/>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr"/>
-      <c r="G4" t="inlineStr"/>
+          <t>QVJwrCwI</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>jaQQ0fMu</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>kelati andu yobel</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>EkcE3L0c</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>skrzybski steven</t>
+        </is>
+      </c>
       <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>lla8DJW0</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>amoura mohamed</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>pleKaexP</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>bialek bartosz</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>QscOyy8Q</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>maehle joakim</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>6D2Vm8M8</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>nmecha lukas</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>lIg2Sr9i</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>paredes kevin</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>OrlbhXJo</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>QVJwrCwI</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr"/>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr"/>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+          <t>61DvZGfm</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>63mrBJnS</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>al dakhil ameen</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ja18uZOO</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>nartey nikolas</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>YFNUTMWH</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>raimund luca</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>hCWLxEzr</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>rouault anthony</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>pIMPjP8B</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>jenz moritz</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>vVKqrtep</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>stergiou leonidas</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>61DvZGfm</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr"/>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+          <t>0OYDmG9t</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>4MB78NvI</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>keita naby</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>4pESGQSm</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>pieper amos</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr"/>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>fVyb9zlg</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>couto yan</t>
+        </is>
+      </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>0OYDmG9t</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr"/>
-      <c r="C7" t="inlineStr"/>
+          <t>AVR8vwXP</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>xEflXBhr</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>palacios exequiel</t>
+        </is>
+      </c>
       <c r="D7" t="inlineStr"/>
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
       <c r="H7" t="inlineStr"/>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>6DL0LD7a</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>bitshiabu el chadaille</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>WQdSnUfq</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>orban willi</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>bs71GRSt</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>ouedraogo assan</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>AVR8vwXP</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr"/>
-      <c r="C8" t="inlineStr"/>
+          <t>W8b4TCOO</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>vTDGEfNG</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>keller thomas</t>
+        </is>
+      </c>
       <c r="D8" t="inlineStr"/>
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr"/>
       <c r="H8" t="inlineStr"/>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr"/>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bi35uzgT</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>dahmen finn</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>OKcwlyhN</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>framberger raphael</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>x8uj789H</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>gumny robert</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>QkJGjOO2</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>jakic kristijan</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+          <t>2T6mXfPa</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>fw8tPLtH</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>ibrahimovic arijon</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>MVgAbUb4</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>daniel peretz</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>UwlvfZCm</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>atubolu noah</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>fNPBHb0p</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>gregoritsch michael</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>bLZ4JBQc</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>gulde manuel</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>GdruQez1</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>schmidt kenneth</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>GlTyfr8U</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>sane leroy</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>WCM2C2l0</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>sildillia kiliann</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
+          <t>zsmd0ggn</t>
         </is>
       </c>
       <c r="B10" t="inlineStr"/>
@@ -744,6 +1300,216 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,384 +425,69 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AE3"/>
+  <dimension ref="A2:A10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AB1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_8</t>
-        </is>
-      </c>
-      <c r="AC1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_8</t>
-        </is>
-      </c>
-      <c r="AD1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_9</t>
-        </is>
-      </c>
-      <c r="AE1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_9</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>W8b4TCOO</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>vTDGEfNG</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>keller thomas</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>bi35uzgT</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>dahmen finn</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>OKcwlyhN</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>framberger raphael</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>x8uj789H</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>gumny robert</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
-      <c r="AB2" t="inlineStr"/>
-      <c r="AC2" t="inlineStr"/>
-      <c r="AD2" t="inlineStr"/>
-      <c r="AE2" t="inlineStr"/>
+          <t>zsmd0ggn</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>2T6mXfPa</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>dAlY7ECt</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>buchmann tarek</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>UwlvfZCm</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>atubolu noah</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>tATOM8P9</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>dinkci eren</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>tprC8Q14</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>ezekwem kimberly</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>fw8tPLtH</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>ibrahimovic arijon</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>4ULsVw9c</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>ito hiroki</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>MVgAbUb4</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>daniel peretz</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>GlTyfr8U</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>sane leroy</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>SfawK0Y3</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>stanisic josip</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>fNPBHb0p</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>gregoritsch michael</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>bLZ4JBQc</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>gulde manuel</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>tUPHhVGD</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>kyereh daniel kofi</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>6PCSjJja</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>philipp maximilian</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>GdruQez1</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>schmidt kenneth</t>
-        </is>
-      </c>
-      <c r="AD3" t="inlineStr">
-        <is>
-          <t>WCM2C2l0</t>
-        </is>
-      </c>
-      <c r="AE3" t="inlineStr">
-        <is>
-          <t>sildillia kiliann</t>
+          <t>UwsvBA74</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>vZqDdBhB</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>r7j4bXNb</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>WSMotj8U</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>tI0qkTpo</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>x4pn9lxH</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8OhVCWxh</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A10"/>
+  <dimension ref="A2:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="2">
@@ -491,6 +491,69 @@
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>dCL13J5e</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,134 +425,232 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:Q3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>zsmd0ggn</t>
+          <t>CnrLfkNN</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>bi35uzgT</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>dahmen finn</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>OKcwlyhN</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>framberger raphael</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>x8uj789H</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>gumny robert</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>QwxAZ5yD</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>burchert sascha</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>zqXaHPUa</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>metcalfe connor</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>remhb0a6</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>smith eric</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>rD3WL6oI</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>zoller simon</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>UwsvBA74</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>vZqDdBhB</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>r7j4bXNb</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>WSMotj8U</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="inlineStr">
-        <is>
-          <t>tI0qkTpo</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>x4pn9lxH</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="1" t="inlineStr">
-        <is>
-          <t>CnrLfkNN</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
           <t>8OhVCWxh</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>dCL13J5e</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>pY1dP0SE</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>QNoNA1DL</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>hvFA1cz8</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>AeNg5uyq</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>IcrFCNr9</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>Uy2KjtMk</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>2k0SlKj2</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>dQ0zIIKl</t>
-        </is>
-      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ru11TuPI</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>hanche olsen andreas</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>lbqsZvEf</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>burke oliver</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>4MB78NvI</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>keita naby</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>E7uclPCf</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>veljkovic milos</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,232 +425,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A2:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>bi35uzgT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>dahmen finn</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>OKcwlyhN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>framberger raphael</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>x8uj789H</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>gumny robert</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>6y5I2kuT</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ahlers soren</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>QwxAZ5yD</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>burchert sascha</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>zqXaHPUa</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>metcalfe connor</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>remhb0a6</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>smith eric</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>rD3WL6oI</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>zoller simon</t>
+          <t>dCL13J5e</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ru11TuPI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>hanche olsen andreas</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>lbqsZvEf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>burke oliver</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4MB78NvI</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>keita naby</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>E7uclPCf</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>veljkovic milos</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>dQ0zIIKl</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>rsNyMnwK</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,132 +425,898 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:AA9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>dCL13J5e</t>
-        </is>
-      </c>
+          <t>pY1dP0SE</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>MwxzFrgA</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>bernardo</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>0bSbpzks</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>miyoshi koji</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>40wafXg4</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>ordets ivan</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>dGcprQ0r</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>riemann manuel</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>xfKprpfm</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>erras patrick</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>pY1dP0SE</t>
-        </is>
-      </c>
+          <t>QNoNA1DL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>EuU2yU29</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>feller frank</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>vTDGEfNG</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>keller thomas</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>fNPBHb0p</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>gregoritsch michael</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>bLZ4JBQc</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>gulde manuel</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>6PCSjJja</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>philipp maximilian</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>b7FJ7Yb9</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>QNoNA1DL</t>
-        </is>
-      </c>
+          <t>hvFA1cz8</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Oh6gIVja</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>stein yannic</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>tbJx15yJ</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>bebou ihlas</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>OrIOjLpG</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2FUsDXpd</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>hlozek adam</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>6V0rWuu1</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>kramaric andrej</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>d0ASdOqf</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>lenz christopher</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>GOTDkA9I</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>promel grischa</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>hvFA1cz8</t>
-        </is>
-      </c>
+          <t>AeNg5uyq</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>lbqsZvEf</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>burke oliver</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2FUXXkKc</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>deman olivier</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>MkHz7wta</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>gideon justin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>E7uclPCf</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>veljkovic milos</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>zJ9nejml</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>boey sacha</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>fw8tPLtH</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>ibrahimovic arijon</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>MVgAbUb4</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>daniel peretz</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>AeNg5uyq</t>
-        </is>
-      </c>
+          <t>IcrFCNr9</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>veaF8P5m</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gotze mario</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>QqugudYS</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>trapp kevin</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>ltDOVSGt</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>borges sanches yvandro</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>pWiv7csf</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>honorat franck</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>MyyplBl4</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>olschowsky jan</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>IwP3NZs5</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>omlin jonas</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>pYy1apYK</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>wenig marcel</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>IcrFCNr9</t>
-        </is>
-      </c>
+          <t>Uy2KjtMk</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>pleKaexP</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>bialek bartosz</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>QscOyy8Q</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>maehle joakim</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>444Jw1Mr</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>majer lovro</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6D2Vm8M8</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>nmecha lukas</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>lIg2Sr9i</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>paredes kevin</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>OrlbhXJo</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Uy2KjtMk</t>
-        </is>
-      </c>
+          <t>2k0SlKj2</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>63mrBJnS</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>al dakhil ameen</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>ja18uZOO</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>nartey nikolas</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>zF5Q2DOk</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>reyna giovanni</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>2k0SlKj2</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="1" t="inlineStr">
-        <is>
           <t>dQ0zIIKl</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>rsNyMnwK</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>CIlrT3pm</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>6uSGCr06</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>f18BYPMP</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Q5hiEzKD</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>SfGPAMUI</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>IukqGdk1</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>pWnjRsFa</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>bFO8E4Vg</t>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>QwxAZ5yD</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>burchert sascha</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>rVehg4DU</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>guilavogui morgan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>zqXaHPUa</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>metcalfe connor</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ttXwlOTi</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>kampl kevin</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>bs71GRSt</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>ouedraogo assan</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>rcSN3FVD</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>saad elias</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>rD3WL6oI</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>zoller simon</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,232 +425,134 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q3"/>
+  <dimension ref="A2:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>CnrLfkNN</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>bi35uzgT</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>dahmen finn</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>OKcwlyhN</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>framberger raphael</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>x8uj789H</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>gumny robert</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>6y5I2kuT</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>ahlers soren</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>QwxAZ5yD</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>burchert sascha</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>zqXaHPUa</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>metcalfe connor</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>remhb0a6</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>smith eric</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>rD3WL6oI</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
-        <is>
-          <t>zoller simon</t>
+          <t>rsNyMnwK</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>8OhVCWxh</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>ru11TuPI</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>hanche olsen andreas</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr"/>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>lbqsZvEf</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>burke oliver</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4MB78NvI</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>keita naby</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>E7uclPCf</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>veljkovic milos</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
+          <t>CIlrT3pm</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>6uSGCr06</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>f18BYPMP</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>Q5hiEzKD</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>SfGPAMUI</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>IukqGdk1</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>pWnjRsFa</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>bFO8E4Vg</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>UajsPCkT</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,213 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:AA10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>rsNyMnwK</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>80RErj9O</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>nmecha felix</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>zF5Q2DOk</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>reyna giovanni</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>MwxzFrgA</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>bernardo</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>SM5LWds5</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>masovic erhan</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>4bt7xopA</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>tolba mohammed</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" t="inlineStr"/>
+      <c r="Q2" t="inlineStr"/>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +639,96 @@
           <t>CIlrT3pm</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ltDOVSGt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>borges sanches yvandro</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pWiv7csf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>honorat franck</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WdkYVaj9</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>prtajin ivan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>Oh6gIVja</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>stein yannic</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>MyyplBl4</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>olschowsky jan</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>IwP3NZs5</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>omlin jonas</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +736,104 @@
           <t>6uSGCr06</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>QwxAZ5yD</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>burchert sascha</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>rVehg4DU</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>guilavogui morgan</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>b7FJ7Yb9</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>WCM2C2l0</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>sildillia kiliann</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>jZFOfyk2</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>maurides</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>rD3WL6oI</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>zoller simon</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +841,48 @@
           <t>f18BYPMP</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>b3H5VR8I</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>amiri nadiem</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>vTDGEfNG</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>keller thomas</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +890,96 @@
           <t>Q5hiEzKD</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>ttXwlOTi</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>kampl kevin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bs71GRSt</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>ouedraogo assan</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>bi35uzgT</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>dahmen finn</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>WUr4kj1n</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>essende samuel</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>OKcwlyhN</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>framberger raphael</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>x8uj789H</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>gumny robert</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>8dDPou3m</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>klein daniel</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +987,112 @@
           <t>SfGPAMUI</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>pleKaexP</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bialek bartosz</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>rZTSn6gr</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>gerhardt yannick</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>QscOyy8Q</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>maehle joakim</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>444Jw1Mr</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>majer lovro</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>6D2Vm8M8</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>nmecha lukas</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>lIg2Sr9i</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>paredes kevin</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>OrlbhXJo</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>WSswmxBa</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>tiago tomas</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1100,72 @@
           <t>IukqGdk1</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>zJ9nejml</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>boey sacha</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>fw8tPLtH</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>ibrahimovic arijon</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1173,80 @@
           <t>pWnjRsFa</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>0Ah8TRF1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>bernhardsson alexander</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>xfKprpfm</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>erras patrick</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>QqugudYS</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>trapp kevin</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,69 +1254,96 @@
           <t>bFO8E4Vg</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>UajsPCkT</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>tbtaPLqC</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>ENOasf5c</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>lpXDJjDj</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>dnhZQYKG</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>zwD8uYZ9</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>0KbQSfj4</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>ShoJUGLi</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>nc8W6DTp</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>tbJx15yJ</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>bebou ihlas</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>OrIOjLpG</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>jacFHyR9</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>friedl marco</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>MkHz7wta</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>gideon justin</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>E7uclPCf</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>veljkovic milos</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>GtZAyRi8</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>geiger dennis</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>GOTDkA9I</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>promel grischa</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S3"/>
+  <dimension ref="A1:AE16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,64 +451,64 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
-        </is>
-      </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
@@ -517,162 +517,1231 @@
       <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>pWnjRsFa</t>
+          <t>UajsPCkT</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>xfKprpfm</t>
+          <t>WUr4kj1n</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>erras patrick</t>
+          <t>essende samuel</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>O4aDKvnH</t>
+          <t>OKcwlyhN</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>kleine bekel colin noah</t>
+          <t>framberger raphael</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>WWSwmP1d</t>
+          <t>x8uj789H</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>hojlund oscar</t>
+          <t>gumny robert</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>4MlIIRDU</t>
+          <t>8dDPou3m</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>loune mehdi</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
+          <t>klein daniel</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>6iPxFKjf</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>pedersen mads</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>U7XUxOei</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>vargas ruben</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ltDOVSGt</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>borges sanches yvandro</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>pWiv7csf</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>honorat franck</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bDOAkNvH</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>ngoumou nathan</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>MyyplBl4</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>olschowsky jan</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>IwP3NZs5</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>omlin jonas</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>bFO8E4Vg</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
+          <t>tbtaPLqC</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>xfKprpfm</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>erras patrick</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>jaQQ0fMu</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>kelati andu yobel</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ENOasf5c</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>MwxzFrgA</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>bernardo</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>4bt7xopA</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>tolba mohammed</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>pleKaexP</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>bialek bartosz</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Aym7cCCj</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>fischer kilian</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>444Jw1Mr</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>majer lovro</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>6D2Vm8M8</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>nmecha lukas</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>lIg2Sr9i</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>paredes kevin</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>OrlbhXJo</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>z522mgfh</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>svanberg mattias</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>jsOwmeQB</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>wimmer patrick</t>
+        </is>
+      </c>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>lpXDJjDj</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>WdkYVaj9</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>prtajin ivan</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Oh6gIVja</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>stein yannic</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>GvIzwgo8</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>adeyemi karim</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>KOdKXsao</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>malen donyell</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>zF5Q2DOk</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>reyna giovanni</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>dnhZQYKG</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>MkHz7wta</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>gideon justin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>xQzNNXkj</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>stark niklas</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>E7uclPCf</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>veljkovic milos</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>bLZ4JBQc</t>
+        </is>
+      </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>gulde manuel</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>b7FJ7Yb9</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>GdruQez1</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>schmidt kenneth</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>WCM2C2l0</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>sildillia kiliann</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>zwD8uYZ9</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>hpqsBljc</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>boukhalfa carlo</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>QwxAZ5yD</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>burchert sascha</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>jZFOfyk2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>maurides</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>rD3WL6oI</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>zoller simon</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>ru11TuPI</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>hanche olsen andreas</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>0KbQSfj4</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>S679EPOB</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>dorsch niklas</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>j7gY6FJ1</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>honsak mathias</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>pYA5gFTu</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>kaufmann mikkel</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>vTDGEfNG</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>keller thomas</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>80wjP4AN</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>niehues julian</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>rqcu4a9O</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>baumgartner christoph</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>ttXwlOTi</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>kampl kevin</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>bs71GRSt</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>ouedraogo assan</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ShoJUGLi</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>zJ9nejml</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>boey sacha</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>fw8tPLtH</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>ibrahimovic arijon</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>nVzSNrOf</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>musiala jamal</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>nc8W6DTp</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>63mrBJnS</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>al dakhil ameen</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>zc2VFBzR</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>karazor atakan</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>ja18uZOO</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>nartey nikolas</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>vVKqrtep</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>stergiou leonidas</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>MNTqORR3</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>vagnoman josha</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
         <is>
           <t>tbJx15yJ</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
+      <c r="O10" t="inlineStr">
         <is>
           <t>bebou ihlas</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>OrIOjLpG</t>
         </is>
       </c>
-      <c r="E3" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>becker finn ole</t>
         </is>
       </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>jacFHyR9</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>friedl marco</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>MkHz7wta</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>gideon justin</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
+      <c r="R10" t="inlineStr">
         <is>
           <t>GtZAyRi8</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="S10" t="inlineStr">
         <is>
           <t>geiger dennis</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>lxAucZ4d</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gendrey valentin</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
+      <c r="T10" t="inlineStr">
         <is>
           <t>nBbGuPN8</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>kabak ozan</t>
         </is>
       </c>
-      <c r="P3" t="inlineStr">
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>QaQIZA1a</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>nsoki stanley</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
         <is>
           <t>GOTDkA9I</t>
         </is>
       </c>
-      <c r="Q3" t="inlineStr">
+      <c r="Y10" t="inlineStr">
         <is>
           <t>promel grischa</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>E7uclPCf</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>veljkovic milos</t>
-        </is>
-      </c>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>z1eeWTdd</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>fHjVr7t2</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>r3GGwC4M</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>M93rhBJF</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>Eq0zfXl3</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>E7rNpTBk</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,245 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:AA19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>z1eeWTdd</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>GvIzwgo8</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>adeyemi karim</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>G8jmgFZE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>duranville julien</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>zF5Q2DOk</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>reyna giovanni</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>QwxAZ5yD</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>burchert sascha</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>zqXaHPUa</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>metcalfe connor</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>rcSN3FVD</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>saad elias</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>nNQpJoz5</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>voll ben alexander</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>rD3WL6oI</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>zoller simon</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +671,104 @@
           <t>fHjVr7t2</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>ltDOVSGt</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>borges sanches yvandro</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>pWiv7csf</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>honorat franck</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>bDOAkNvH</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ngoumou nathan</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>j7gY6FJ1</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>honsak mathias</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>vTDGEfNG</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>keller thomas</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>80wjP4AN</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>niehues julian</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>MyyplBl4</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>olschowsky jan</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>IwP3NZs5</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>omlin jonas</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +776,56 @@
           <t>r3GGwC4M</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>0Q5gjImi</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>wirtz florian</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +833,112 @@
           <t>M93rhBJF</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>bLZ4JBQc</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>gulde manuel</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>OKcwlyhN</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>framberger raphael</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>x8uj789H</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>gumny robert</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>8dDPou3m</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>klein daniel</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>6iPxFKjf</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>pedersen mads</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>GWq0av19</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>schlotterbeck keven</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>U7XUxOei</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>vargas ruben</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>b7FJ7Yb9</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +946,88 @@
           <t>Eq0zfXl3</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>tbJx15yJ</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>bebou ihlas</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>OrIOjLpG</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>lWQqSFyt</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>bero matus</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>4bt7xopA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>tolba mohammed</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>MwBrqRha</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>kaderabek pavel</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>GOTDkA9I</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>promel grischa</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1035,72 @@
           <t>E7rNpTBk</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>jHU6p6gQ</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>kohr dominik</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>ttXwlOTi</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>kampl kevin</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bs71GRSt</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>ouedraogo assan</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>2XVqEh8k</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>raum david</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1108,128 @@
           <t>2mcmYkSq</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>zJ9nejml</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>boey sacha</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bczcNJFB</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>fuhrich chris</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ja18uZOO</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>nartey nikolas</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>YFNUTMWH</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>raimund luca</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>vVKqrtep</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>stergiou leonidas</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>MNTqORR3</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>vagnoman josha</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>nVzSNrOf</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>musiala jamal</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1237,32 @@
           <t>nBwH6AY8</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +1270,32 @@
           <t>rPiijklS</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -497,6 +1303,32 @@
           <t>4E8uaJWa</t>
         </is>
       </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -504,6 +1336,32 @@
           <t>x0haJmIE</t>
         </is>
       </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -511,6 +1369,32 @@
           <t>ELNeaSQr</t>
         </is>
       </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -518,6 +1402,32 @@
           <t>Mku6FvHt</t>
         </is>
       </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -525,6 +1435,32 @@
           <t>rwXP4l3L</t>
         </is>
       </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -532,6 +1468,32 @@
           <t>MiACepQ7</t>
         </is>
       </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -539,6 +1501,32 @@
           <t>WQadeyWO</t>
         </is>
       </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -546,6 +1534,32 @@
           <t>ABBmcc1C</t>
         </is>
       </c>
+      <c r="B18" t="inlineStr"/>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr"/>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" t="inlineStr"/>
+      <c r="Q18" t="inlineStr"/>
+      <c r="R18" t="inlineStr"/>
+      <c r="S18" t="inlineStr"/>
+      <c r="T18" t="inlineStr"/>
+      <c r="U18" t="inlineStr"/>
+      <c r="V18" t="inlineStr"/>
+      <c r="W18" t="inlineStr"/>
+      <c r="X18" t="inlineStr"/>
+      <c r="Y18" t="inlineStr"/>
+      <c r="Z18" t="inlineStr"/>
+      <c r="AA18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -553,6 +1567,32 @@
           <t>zyC4c6ee</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr"/>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr"/>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr"/>
+      <c r="N19" t="inlineStr"/>
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" t="inlineStr"/>
+      <c r="Q19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr"/>
+      <c r="T19" t="inlineStr"/>
+      <c r="U19" t="inlineStr"/>
+      <c r="V19" t="inlineStr"/>
+      <c r="W19" t="inlineStr"/>
+      <c r="X19" t="inlineStr"/>
+      <c r="Y19" t="inlineStr"/>
+      <c r="Z19" t="inlineStr"/>
+      <c r="AA19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA19"/>
+  <dimension ref="A1:AE19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,102 +461,122 @@
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_away_1</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_1</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_2</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_3</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_3</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_4</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="Q1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_4</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="R1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_5</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="S1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_5</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="T1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_away_6</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_away_6</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
       <c r="V1" s="1" t="inlineStr">
         <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
           <t>id_player_miss_home_5</t>
         </is>
       </c>
-      <c r="W1" s="1" t="inlineStr">
+      <c r="AA1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_5</t>
         </is>
       </c>
-      <c r="X1" s="1" t="inlineStr">
+      <c r="AB1" s="1" t="inlineStr">
         <is>
           <t>id_player_miss_home_6</t>
         </is>
       </c>
-      <c r="Y1" s="1" t="inlineStr">
+      <c r="AC1" s="1" t="inlineStr">
         <is>
           <t>player_name_miss_home_6</t>
         </is>
       </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_7</t>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
         </is>
       </c>
     </row>
@@ -578,92 +598,120 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
+          <t>fVyb9zlg</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>couto yan</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
           <t>G8jmgFZE</t>
         </is>
       </c>
-      <c r="E2" t="inlineStr">
+      <c r="G2" t="inlineStr">
         <is>
           <t>duranville julien</t>
         </is>
       </c>
-      <c r="F2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>zF5Q2DOk</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="I2" t="inlineStr">
         <is>
           <t>reyna giovanni</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr">
+      <c r="J2" t="inlineStr">
         <is>
           <t>6y5I2kuT</t>
         </is>
       </c>
-      <c r="I2" t="inlineStr">
+      <c r="K2" t="inlineStr">
         <is>
           <t>ahlers soren</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hpqsBljc</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>boukhalfa carlo</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
         <is>
           <t>QwxAZ5yD</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="O2" t="inlineStr">
         <is>
           <t>burchert sascha</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>zqXaHPUa</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>metcalfe connor</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="R2" t="inlineStr">
         <is>
           <t>rcSN3FVD</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="S2" t="inlineStr">
         <is>
           <t>saad elias</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>OnSOMqye</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>sinani danel</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
         <is>
           <t>nNQpJoz5</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="W2" t="inlineStr">
         <is>
           <t>voll ben alexander</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="X2" t="inlineStr">
         <is>
           <t>rD3WL6oI</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
+      <c r="Y2" t="inlineStr">
         <is>
           <t>zoller simon</t>
         </is>
       </c>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
       <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -683,92 +731,96 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>pWiv7csf</t>
+          <t>bDOAkNvH</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>honorat franck</t>
+          <t>ngoumou nathan</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>bDOAkNvH</t>
+          <t>MyyplBl4</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>ngoumou nathan</t>
+          <t>olschowsky jan</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>IwP3NZs5</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>omlin jonas</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>S679EPOB</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>dorsch niklas</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
           <t>j7gY6FJ1</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
+      <c r="M3" t="inlineStr">
         <is>
           <t>honsak mathias</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr">
+      <c r="N3" t="inlineStr">
         <is>
           <t>vTDGEfNG</t>
         </is>
       </c>
-      <c r="K3" t="inlineStr">
+      <c r="O3" t="inlineStr">
         <is>
           <t>keller thomas</t>
         </is>
       </c>
-      <c r="L3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>80wjP4AN</t>
         </is>
       </c>
-      <c r="M3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>niehues julian</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr"/>
       <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>MyyplBl4</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>olschowsky jan</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>IwP3NZs5</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>omlin jonas</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr">
         <is>
           <t>ruMn6c8t</t>
         </is>
       </c>
-      <c r="Y3" t="inlineStr">
+      <c r="AA3" t="inlineStr">
         <is>
           <t>walde simon</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -790,28 +842,28 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr"/>
       <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr">
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr">
         <is>
           <t>WWSwmP1d</t>
         </is>
       </c>
-      <c r="I4" t="inlineStr">
+      <c r="K4" t="inlineStr">
         <is>
           <t>hojlund oscar</t>
         </is>
       </c>
-      <c r="J4" t="inlineStr">
+      <c r="L4" t="inlineStr">
         <is>
           <t>4MlIIRDU</t>
         </is>
       </c>
-      <c r="K4" t="inlineStr">
+      <c r="M4" t="inlineStr">
         <is>
           <t>loune mehdi</t>
         </is>
       </c>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
       <c r="P4" t="inlineStr"/>
@@ -826,6 +878,10 @@
       <c r="Y4" t="inlineStr"/>
       <c r="Z4" t="inlineStr"/>
       <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -845,92 +901,84 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>bLZ4JBQc</t>
+          <t>tUPHhVGD</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>gulde manuel</t>
+          <t>kyereh daniel kofi</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>tUPHhVGD</t>
+          <t>b7FJ7Yb9</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>kyereh daniel kofi</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
         <is>
           <t>OKcwlyhN</t>
         </is>
       </c>
-      <c r="I5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>framberger raphael</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr">
+      <c r="L5" t="inlineStr">
         <is>
           <t>x8uj789H</t>
         </is>
       </c>
-      <c r="K5" t="inlineStr">
+      <c r="M5" t="inlineStr">
         <is>
           <t>gumny robert</t>
         </is>
       </c>
-      <c r="L5" t="inlineStr">
+      <c r="N5" t="inlineStr">
         <is>
           <t>8dDPou3m</t>
         </is>
       </c>
-      <c r="M5" t="inlineStr">
+      <c r="O5" t="inlineStr">
         <is>
           <t>klein daniel</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>6iPxFKjf</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
+      <c r="Q5" t="inlineStr">
         <is>
           <t>pedersen mads</t>
         </is>
       </c>
-      <c r="P5" t="inlineStr">
+      <c r="R5" t="inlineStr">
         <is>
           <t>GWq0av19</t>
         </is>
       </c>
-      <c r="Q5" t="inlineStr">
+      <c r="S5" t="inlineStr">
         <is>
           <t>schlotterbeck keven</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="T5" t="inlineStr">
         <is>
           <t>U7XUxOei</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>vargas ruben</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>b7FJ7Yb9</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>rohl merlin</t>
         </is>
       </c>
       <c r="V5" t="inlineStr"/>
@@ -939,6 +987,10 @@
       <c r="Y5" t="inlineStr"/>
       <c r="Z5" t="inlineStr"/>
       <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -968,66 +1020,102 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
+          <t>GtZAyRi8</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>geiger dennis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
           <t>nBbGuPN8</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="I6" t="inlineStr">
         <is>
           <t>kabak ozan</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr">
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>MwxzFrgA</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>bernardo</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
         <is>
           <t>lWQqSFyt</t>
         </is>
       </c>
-      <c r="I6" t="inlineStr">
+      <c r="M6" t="inlineStr">
         <is>
           <t>bero matus</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr">
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>GE24QNxi</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>boadu myron</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
         <is>
           <t>4bt7xopA</t>
         </is>
       </c>
-      <c r="K6" t="inlineStr">
+      <c r="Q6" t="inlineStr">
         <is>
           <t>tolba mohammed</t>
         </is>
       </c>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
-      <c r="P6" t="inlineStr"/>
-      <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr"/>
       <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>MwBrqRha</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>kaderabek pavel</t>
-        </is>
-      </c>
-      <c r="V6" t="inlineStr">
-        <is>
-          <t>GOTDkA9I</t>
-        </is>
-      </c>
-      <c r="W6" t="inlineStr">
-        <is>
-          <t>promel grischa</t>
-        </is>
-      </c>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
       <c r="X6" t="inlineStr"/>
       <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>MwBrqRha</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>kaderabek pavel</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>QaQIZA1a</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>nsoki stanley</t>
+        </is>
+      </c>
+      <c r="AD6" t="inlineStr">
+        <is>
+          <t>GOTDkA9I</t>
+        </is>
+      </c>
+      <c r="AE6" t="inlineStr">
+        <is>
+          <t>promel grischa</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -1045,52 +1133,60 @@
           <t>kohr dominik</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>lnXQSLq2</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>onisiwo karim</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr"/>
       <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>ttXwlOTi</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>kampl kevin</t>
-        </is>
-      </c>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
+          <t>xEK5LMdo</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>henrichs benjamin</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
           <t>bs71GRSt</t>
         </is>
       </c>
-      <c r="K7" t="inlineStr">
+      <c r="M7" t="inlineStr">
         <is>
           <t>ouedraogo assan</t>
         </is>
       </c>
-      <c r="L7" t="inlineStr">
+      <c r="N7" t="inlineStr">
         <is>
           <t>2XVqEh8k</t>
         </is>
       </c>
-      <c r="M7" t="inlineStr">
+      <c r="O7" t="inlineStr">
         <is>
           <t>raum david</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>M1bcCLIU</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
+      <c r="Q7" t="inlineStr">
         <is>
           <t>schlager xaver</t>
         </is>
       </c>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr"/>
       <c r="S7" t="inlineStr"/>
       <c r="T7" t="inlineStr"/>
@@ -1101,6 +1197,10 @@
       <c r="Y7" t="inlineStr"/>
       <c r="Z7" t="inlineStr"/>
       <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -1140,96 +1240,100 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
+          <t>nVzSNrOf</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>musiala jamal</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
           <t>tSVfwjYd</t>
         </is>
       </c>
-      <c r="I8" t="inlineStr">
+      <c r="K8" t="inlineStr">
         <is>
           <t>diehl justin</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr">
+      <c r="L8" t="inlineStr">
         <is>
           <t>bczcNJFB</t>
         </is>
       </c>
-      <c r="K8" t="inlineStr">
+      <c r="M8" t="inlineStr">
         <is>
           <t>fuhrich chris</t>
         </is>
       </c>
-      <c r="L8" t="inlineStr">
+      <c r="N8" t="inlineStr">
         <is>
           <t>ja18uZOO</t>
         </is>
       </c>
-      <c r="M8" t="inlineStr">
+      <c r="O8" t="inlineStr">
         <is>
           <t>nartey nikolas</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>YFNUTMWH</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
+      <c r="Q8" t="inlineStr">
         <is>
           <t>raimund luca</t>
         </is>
       </c>
-      <c r="P8" t="inlineStr">
+      <c r="R8" t="inlineStr">
         <is>
           <t>vVKqrtep</t>
         </is>
       </c>
-      <c r="Q8" t="inlineStr">
+      <c r="S8" t="inlineStr">
         <is>
           <t>stergiou leonidas</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
-        <is>
-          <t>MNTqORR3</t>
-        </is>
-      </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>vagnoman josha</t>
-        </is>
-      </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>nVzSNrOf</t>
+          <t>j1IjJkHI</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>musiala jamal</t>
-        </is>
-      </c>
-      <c r="V8" t="inlineStr">
-        <is>
-          <t>SfawK0Y3</t>
-        </is>
-      </c>
-      <c r="W8" t="inlineStr">
-        <is>
-          <t>stanisic josip</t>
-        </is>
-      </c>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
       <c r="X8" t="inlineStr"/>
       <c r="Y8" t="inlineStr"/>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>j1IjJkHI</t>
+          <t>SfawK0Y3</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>zagadou dan axel</t>
-        </is>
-      </c>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>OMhLhEJB</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>upamecano dayot</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -1237,22 +1341,78 @@
           <t>nBwH6AY8</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr"/>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr"/>
-      <c r="G9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>4lxZ6TzS</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>johansson carl</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>jaQQ0fMu</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>kelati andu yobel</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
       <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
-      <c r="P9" t="inlineStr"/>
-      <c r="Q9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>WdkYVaj9</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>prtajin ivan</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>Oh6gIVja</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
+          <t>stein yannic</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>dnpDxpQf</t>
+        </is>
+      </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>volland kevin</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr"/>
       <c r="S9" t="inlineStr"/>
       <c r="T9" t="inlineStr"/>
@@ -1263,6 +1423,10 @@
       <c r="Y9" t="inlineStr"/>
       <c r="Z9" t="inlineStr"/>
       <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -1296,6 +1460,10 @@
       <c r="Y10" t="inlineStr"/>
       <c r="Z10" t="inlineStr"/>
       <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
@@ -1329,6 +1497,10 @@
       <c r="Y11" t="inlineStr"/>
       <c r="Z11" t="inlineStr"/>
       <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
@@ -1362,6 +1534,10 @@
       <c r="Y12" t="inlineStr"/>
       <c r="Z12" t="inlineStr"/>
       <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
@@ -1395,6 +1571,10 @@
       <c r="Y13" t="inlineStr"/>
       <c r="Z13" t="inlineStr"/>
       <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
@@ -1428,6 +1608,10 @@
       <c r="Y14" t="inlineStr"/>
       <c r="Z14" t="inlineStr"/>
       <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
@@ -1461,6 +1645,10 @@
       <c r="Y15" t="inlineStr"/>
       <c r="Z15" t="inlineStr"/>
       <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
@@ -1494,6 +1682,10 @@
       <c r="Y16" t="inlineStr"/>
       <c r="Z16" t="inlineStr"/>
       <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
@@ -1527,6 +1719,10 @@
       <c r="Y17" t="inlineStr"/>
       <c r="Z17" t="inlineStr"/>
       <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
@@ -1560,6 +1756,10 @@
       <c r="Y18" t="inlineStr"/>
       <c r="Z18" t="inlineStr"/>
       <c r="AA18" t="inlineStr"/>
+      <c r="AB18" t="inlineStr"/>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr"/>
+      <c r="AE18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
@@ -1593,6 +1793,10 @@
       <c r="Y19" t="inlineStr"/>
       <c r="Z19" t="inlineStr"/>
       <c r="AA19" t="inlineStr"/>
+      <c r="AB19" t="inlineStr"/>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr"/>
+      <c r="AE19" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,364 +425,132 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA3"/>
+  <dimension ref="A2:A19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_1</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_1</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_2</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_2</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_3</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_3</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_1</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_2</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_2</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_3</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_3</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_4</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_4</t>
-        </is>
-      </c>
-      <c r="P1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_4</t>
-        </is>
-      </c>
-      <c r="Q1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_4</t>
-        </is>
-      </c>
-      <c r="R1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_5</t>
-        </is>
-      </c>
-      <c r="S1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_5</t>
-        </is>
-      </c>
-      <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_home_6</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_home_6</t>
-        </is>
-      </c>
-      <c r="V1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_5</t>
-        </is>
-      </c>
-      <c r="W1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_5</t>
-        </is>
-      </c>
-      <c r="X1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_6</t>
-        </is>
-      </c>
-      <c r="Y1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_6</t>
-        </is>
-      </c>
-      <c r="Z1" s="1" t="inlineStr">
-        <is>
-          <t>id_player_miss_away_7</t>
-        </is>
-      </c>
-      <c r="AA1" s="1" t="inlineStr">
-        <is>
-          <t>player_name_miss_away_7</t>
-        </is>
-      </c>
-    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>nBwH6AY8</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>4lxZ6TzS</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>johansson carl</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>jaQQ0fMu</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>kelati andu yobel</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>O4aDKvnH</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>kleine bekel colin noah</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>WznPyl4k</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>juranovic josip</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>YJUO3rKf</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>tousart lucas</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>WdkYVaj9</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>prtajin ivan</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>dnpDxpQf</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>volland kevin</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="inlineStr"/>
-      <c r="R2" t="inlineStr"/>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr"/>
-      <c r="V2" t="inlineStr"/>
-      <c r="W2" t="inlineStr"/>
-      <c r="X2" t="inlineStr"/>
-      <c r="Y2" t="inlineStr"/>
-      <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr"/>
+          <t>4E8uaJWa</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>rPiijklS</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>pleKaexP</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>bialek bartosz</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>444Jw1Mr</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>majer lovro</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>6D2Vm8M8</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>nmecha lukas</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>WlEZExcF</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>alvero skelly</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>4MB78NvI</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>keita naby</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>MkHz7wta</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>gideon justin</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>jJ1sdqU7</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>stage jens</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>lIg2Sr9i</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>paredes kevin</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>OrlbhXJo</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>rogerio</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>z522mgfh</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>svanberg mattias</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>xQzNNXkj</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>stark niklas</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>E7uclPCf</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>veljkovic milos</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>hIljeTIQ</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>lynen senne</t>
+          <t>x0haJmIE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>ELNeaSQr</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>Mku6FvHt</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="inlineStr">
+        <is>
+          <t>rwXP4l3L</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>MiACepQ7</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="inlineStr">
+        <is>
+          <t>WQadeyWO</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="inlineStr">
+        <is>
+          <t>ABBmcc1C</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>zyC4c6ee</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>IHYEDIog</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>jVWMBdG5</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>485V7EFU</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>8MVuSH0n</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>2q7yHiho</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>AoSdOZaB</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>dr2N9zoI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="inlineStr">
+        <is>
+          <t>GnZmQeVb</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>raQ4MDUN</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,281 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:AG10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_9</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_9</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>4E8uaJWa</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>ru11TuPI</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>hanche olsen andreas</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>lnXQSLq2</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>onisiwo karim</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>ltDOVSGt</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>borges sanches yvandro</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>YZUjjz4A</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>netz luca</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>bDOAkNvH</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>ngoumou nathan</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>MyyplBl4</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>olschowsky jan</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>fZO9OHIM</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>elvedi nico</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>IwP3NZs5</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>omlin jonas</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +707,126 @@
           <t>x0haJmIE</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>OKcwlyhN</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>framberger raphael</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>KC0NKT7S</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>oxford reece</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>GvIzwgo8</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>adeyemi karim</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>fVyb9zlg</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>couto yan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>G8jmgFZE</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>duranville julien</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>zF5Q2DOk</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>reyna giovanni</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>8nv0ZZYK</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>ryerson julian</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>G43Lp4in</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>sule niklas</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>GWq0av19</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>schlotterbeck keven</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>U7XUxOei</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>vargas ruben</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>x8uj789H</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>gumny robert</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +834,126 @@
           <t>ELNeaSQr</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>KI3jSJTG</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>klostermann lukas</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2XVqEh8k</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>raum david</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>b7FJ7Yb9</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>bLZ4JBQc</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>gulde manuel</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>GdruQez1</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>schmidt kenneth</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>fivkoAh0</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>seiwald nicolas</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>noo0L9zk</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>simons xavi</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>bs71GRSt</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>ouedraogo assan</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +961,158 @@
           <t>Mku6FvHt</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>zqXaHPUa</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>metcalfe connor</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>pUChj7Xb</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>arnold maximilian</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>pleKaexP</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>bialek bartosz</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>444Jw1Mr</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>majer lovro</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>6D2Vm8M8</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>nmecha lukas</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>lIg2Sr9i</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>paredes kevin</t>
+        </is>
+      </c>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>OrlbhXJo</t>
+        </is>
+      </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>jsOwmeQB</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>wimmer patrick</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>rcSN3FVD</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>saad elias</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>nNQpJoz5</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>voll ben alexander</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>hpqsBljc</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>boukhalfa carlo</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>remhb0a6</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>smith eric</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>zXOjivLH</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>treu philipp</t>
+        </is>
+      </c>
+      <c r="AD5" t="inlineStr">
+        <is>
+          <t>z522mgfh</t>
+        </is>
+      </c>
+      <c r="AE5" t="inlineStr">
+        <is>
+          <t>svanberg mattias</t>
+        </is>
+      </c>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1120,118 @@
           <t>rwXP4l3L</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>bczcNJFB</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>fuhrich chris</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>EDemoJW7</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>holtby lewis</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>4lxZ6TzS</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>johansson carl</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>jaQQ0fMu</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>kelati andu yobel</t>
+        </is>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>ja18uZOO</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>nartey nikolas</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>YFNUTMWH</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>raimund luca</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>vVKqrtep</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>stergiou leonidas</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1239,94 @@
           <t>MiACepQ7</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>WlEZExcF</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>alvero skelly</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>4MB78NvI</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>keita naby</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>82ETy0Me</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>adli amine</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>dd4GDL19</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>boniface victor</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>jJ1sdqU7</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>stage jens</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>xQzNNXkj</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>stark niklas</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>hIljeTIQ</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>lynen senne</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1334,118 @@
           <t>WQadeyWO</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>MwxzFrgA</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>bernardo</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>lWQqSFyt</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>bero matus</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>zJ9nejml</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>boey sacha</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>noANPQx4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>pavlovic aleksandar</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>4bt7xopA</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>tolba mohammed</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>GE24QNxi</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>boadu myron</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>vcq6DJJN</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>kwarteng moritz</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1453,102 @@
           <t>ABBmcc1C</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>YJUO3rKf</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>tousart lucas</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>2ebHJb1N</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>knauff ansgar</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>pYy1apYK</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>wenig marcel</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>WdkYVaj9</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>prtajin ivan</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>dnpDxpQf</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>volland kevin</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,67 +1556,116 @@
           <t>zyC4c6ee</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>IHYEDIog</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>jVWMBdG5</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>485V7EFU</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>8MVuSH0n</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>2q7yHiho</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>AoSdOZaB</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>dr2N9zoI</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>GnZmQeVb</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>raQ4MDUN</t>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>vTDGEfNG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>keller thomas</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>tbJx15yJ</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>bebou ihlas</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>OrIOjLpG</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>GOTDkA9I</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>promel grischa</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>KWrYlSTD</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>berisha mergim</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>GtZAyRi8</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>geiger dennis</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>WfACar9B</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>grillitsch florian</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr">
+        <is>
+          <t>AF2Br9IA</t>
+        </is>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>jurasek david</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>MwBrqRha</t>
+        </is>
+      </c>
+      <c r="AG10" t="inlineStr">
+        <is>
+          <t>kaderabek pavel</t>
         </is>
       </c>
     </row>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,293 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A19"/>
+  <dimension ref="A1:AI10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_8</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_9</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_10</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_10</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>IHYEDIog</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>82ETy0Me</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>adli amine</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>zog0NOeM</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>belocian jeanuel</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>f1kf4eiH</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>chabot julian</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ja18uZOO</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>nartey nikolas</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>dSuHglE8</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>fritschi paulo</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>YFNUTMWH</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>raimund luca</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>vVKqrtep</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>stergiou leonidas</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr"/>
+      <c r="AB2" t="inlineStr"/>
+      <c r="AC2" t="inlineStr"/>
+      <c r="AD2" t="inlineStr"/>
+      <c r="AE2" t="inlineStr"/>
+      <c r="AF2" t="inlineStr"/>
+      <c r="AG2" t="inlineStr"/>
+      <c r="AH2" t="inlineStr"/>
+      <c r="AI2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +719,112 @@
           <t>jVWMBdG5</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>zJ9nejml</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>boey sacha</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>WdkYVaj9</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>prtajin ivan</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>YJUO3rKf</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>tousart lucas</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>noANPQx4</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>pavlovic aleksandar</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>OMhLhEJB</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>upamecano dayot</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +832,128 @@
           <t>485V7EFU</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Ii8pjsY2</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>kristensen rasmus</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>U7wepPkr</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>balde aliou</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>MwxzFrgA</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>bernardo</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>GE24QNxi</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>boadu myron</t>
+        </is>
+      </c>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>4bt7xopA</t>
+        </is>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>tolba mohammed</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>lWQqSFyt</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>bero matus</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>2NA43UrT</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>theate arthur</t>
+        </is>
+      </c>
+      <c r="X4" t="inlineStr">
+        <is>
+          <t>pYy1apYK</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>wenig marcel</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>0daEaUg4</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>dina eric</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +961,112 @@
           <t>8MVuSH0n</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>tbJx15yJ</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>bebou ihlas</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>OrIOjLpG</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>nNQpJoz5</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>voll ben alexander</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>zqXaHPUa</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>metcalfe connor</t>
+        </is>
+      </c>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>rcSN3FVD</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>saad elias</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>GOTDkA9I</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>promel grischa</t>
+        </is>
+      </c>
+      <c r="X5" t="inlineStr">
+        <is>
+          <t>GtZAyRi8</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>geiger dennis</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +1074,104 @@
           <t>2q7yHiho</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>bTQKqpWl</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>arp jann fiete</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>0Ah8TRF1</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>bernhardsson alexander</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>nuLsDXY4</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>janes luka</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>vTDGEfNG</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>keller thomas</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>EDemoJW7</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>holtby lewis</t>
+        </is>
+      </c>
+      <c r="X6" t="inlineStr">
+        <is>
+          <t>4lxZ6TzS</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>johansson carl</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>jaQQ0fMu</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>kelati andu yobel</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +1179,152 @@
           <t>AoSdOZaB</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>z58rzyyp</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>bornauw sebastiaan</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>6D2Vm8M8</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>nmecha lukas</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>OKcwlyhN</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>framberger raphael</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>x8uj789H</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>gumny robert</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>YJdpejUK</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>jensen fredrik</t>
+        </is>
+      </c>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>KC0NKT7S</t>
+        </is>
+      </c>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>oxford reece</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>6iPxFKjf</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>pedersen mads</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>U7XUxOei</t>
+        </is>
+      </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>vargas ruben</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>OrlbhXJo</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>jsOwmeQB</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>wimmer patrick</t>
+        </is>
+      </c>
+      <c r="X7" t="inlineStr">
+        <is>
+          <t>pleKaexP</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>bialek bartosz</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>lIg2Sr9i</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>paredes kevin</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>z522mgfh</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>svanberg mattias</t>
+        </is>
+      </c>
+      <c r="AD7" t="inlineStr">
+        <is>
+          <t>EqNGX6pE</t>
+        </is>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>vranckx aster</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +1332,168 @@
           <t>dr2N9zoI</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GvIzwgo8</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>adeyemi karim</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>fVyb9zlg</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>couto yan</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2XVqEh8k</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>raum david</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>noo0L9zk</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>simons xavi</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>IN2MK7Jo</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>openda lois</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>bs71GRSt</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
+          <t>ouedraogo assan</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>fivkoAh0</t>
+        </is>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>seiwald nicolas</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>G8jmgFZE</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>duranville julien</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>p0pBEofo</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>kabar almugera</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>xlBg2ttC</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>kobel gregor</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>zF5Q2DOk</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>reyna giovanni</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>8nv0ZZYK</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>ryerson julian</t>
+        </is>
+      </c>
+      <c r="AD8" t="inlineStr">
+        <is>
+          <t>G43Lp4in</t>
+        </is>
+      </c>
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>sule niklas</t>
+        </is>
+      </c>
+      <c r="AF8" t="inlineStr">
+        <is>
+          <t>Umh5qbVs</t>
+        </is>
+      </c>
+      <c r="AG8" t="inlineStr">
+        <is>
+          <t>watjen kjell</t>
+        </is>
+      </c>
+      <c r="AH8" t="inlineStr">
+        <is>
+          <t>b3gqj94D</t>
+        </is>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>anton waldemar</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +1501,104 @@
           <t>GnZmQeVb</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>bLZ4JBQc</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>gulde manuel</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>MicyKu3h</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>burkardt jonathan</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>ru11TuPI</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>hanche olsen andreas</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>pIMPjP8B</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>jenz moritz</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>b7FJ7Yb9</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="X9" t="inlineStr">
+        <is>
+          <t>GdruQez1</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>schmidt kenneth</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,69 +1606,144 @@
           <t>raQ4MDUN</t>
         </is>
       </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="1" t="inlineStr">
-        <is>
-          <t>v3DAZKP9</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="1" t="inlineStr">
-        <is>
-          <t>biQrHC9r</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="inlineStr">
-        <is>
-          <t>nee3ysec</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="1" t="inlineStr">
-        <is>
-          <t>6HTjFjve</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>YmumZjET</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="1" t="inlineStr">
-        <is>
-          <t>j5mWxZE4</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="1" t="inlineStr">
-        <is>
-          <t>UJQITUyi</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="1" t="inlineStr">
-        <is>
-          <t>UkaNveph</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="1" t="inlineStr">
-        <is>
-          <t>xMovyDqH</t>
-        </is>
-      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>ltDOVSGt</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>borges sanches yvandro</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>YZUjjz4A</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>netz luca</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>hCB1UCHG</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>grull marco</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>4MB78NvI</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>keita naby</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>xQzNNXkj</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>stark niklas</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>WlEZExcF</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>alvero skelly</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>MkHz7wta</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
+          <t>gideon justin</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>jJ1sdqU7</t>
+        </is>
+      </c>
+      <c r="Q10" t="inlineStr">
+        <is>
+          <t>stage jens</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>bDOAkNvH</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>ngoumou nathan</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="X10" t="inlineStr">
+        <is>
+          <t>fZO9OHIM</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>elvedi nico</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>MyyplBl4</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>olschowsky jan</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>IwP3NZs5</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>omlin jonas</t>
+        </is>
+      </c>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
+++ b/data/germany/p6_deployment/data_preparation/clean_data/df_match_player_cleaned.xlsx
@@ -425,15 +425,1069 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A2:A10"/>
+  <dimension ref="A1:DG17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
+    <row r="1">
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_1</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_2</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_2</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_3</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_3</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_4</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_4</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_5</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_5</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_6</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_6</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_7</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_7</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_8</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_8</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_9</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_9</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_10</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_10</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_home_11</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_home_11</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_1</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_1</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_2</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_2</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_3</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_3</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_4</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_4</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_5</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_5</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_6</t>
+        </is>
+      </c>
+      <c r="AI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_6</t>
+        </is>
+      </c>
+      <c r="AJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_7</t>
+        </is>
+      </c>
+      <c r="AK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_7</t>
+        </is>
+      </c>
+      <c r="AL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_8</t>
+        </is>
+      </c>
+      <c r="AM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_8</t>
+        </is>
+      </c>
+      <c r="AN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_9</t>
+        </is>
+      </c>
+      <c r="AO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_9</t>
+        </is>
+      </c>
+      <c r="AP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_10</t>
+        </is>
+      </c>
+      <c r="AQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_10</t>
+        </is>
+      </c>
+      <c r="AR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_start_away_11</t>
+        </is>
+      </c>
+      <c r="AS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_start_away_11</t>
+        </is>
+      </c>
+      <c r="AT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_1</t>
+        </is>
+      </c>
+      <c r="AV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_2</t>
+        </is>
+      </c>
+      <c r="AX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_3</t>
+        </is>
+      </c>
+      <c r="AZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_4</t>
+        </is>
+      </c>
+      <c r="BB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_5</t>
+        </is>
+      </c>
+      <c r="BD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_6</t>
+        </is>
+      </c>
+      <c r="BF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_7</t>
+        </is>
+      </c>
+      <c r="BH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_8</t>
+        </is>
+      </c>
+      <c r="BJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_home_9</t>
+        </is>
+      </c>
+      <c r="BL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_1</t>
+        </is>
+      </c>
+      <c r="BN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_2</t>
+        </is>
+      </c>
+      <c r="BP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_3</t>
+        </is>
+      </c>
+      <c r="BR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_4</t>
+        </is>
+      </c>
+      <c r="BT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_5</t>
+        </is>
+      </c>
+      <c r="BV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_6</t>
+        </is>
+      </c>
+      <c r="BX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_7</t>
+        </is>
+      </c>
+      <c r="BZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_8</t>
+        </is>
+      </c>
+      <c r="CB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_sub_away_9</t>
+        </is>
+      </c>
+      <c r="CD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_1</t>
+        </is>
+      </c>
+      <c r="CE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_1</t>
+        </is>
+      </c>
+      <c r="CF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_2</t>
+        </is>
+      </c>
+      <c r="CG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_2</t>
+        </is>
+      </c>
+      <c r="CH1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_3</t>
+        </is>
+      </c>
+      <c r="CI1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_3</t>
+        </is>
+      </c>
+      <c r="CJ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_1</t>
+        </is>
+      </c>
+      <c r="CK1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_1</t>
+        </is>
+      </c>
+      <c r="CL1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_2</t>
+        </is>
+      </c>
+      <c r="CM1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_2</t>
+        </is>
+      </c>
+      <c r="CN1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_3</t>
+        </is>
+      </c>
+      <c r="CO1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_3</t>
+        </is>
+      </c>
+      <c r="CP1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_4</t>
+        </is>
+      </c>
+      <c r="CQ1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_4</t>
+        </is>
+      </c>
+      <c r="CR1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_5</t>
+        </is>
+      </c>
+      <c r="CS1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_5</t>
+        </is>
+      </c>
+      <c r="CT1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_6</t>
+        </is>
+      </c>
+      <c r="CU1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_6</t>
+        </is>
+      </c>
+      <c r="CV1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_4</t>
+        </is>
+      </c>
+      <c r="CW1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_4</t>
+        </is>
+      </c>
+      <c r="CX1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_5</t>
+        </is>
+      </c>
+      <c r="CY1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_5</t>
+        </is>
+      </c>
+      <c r="CZ1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_7</t>
+        </is>
+      </c>
+      <c r="DA1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_7</t>
+        </is>
+      </c>
+      <c r="DB1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_away_8</t>
+        </is>
+      </c>
+      <c r="DC1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_away_8</t>
+        </is>
+      </c>
+      <c r="DD1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_6</t>
+        </is>
+      </c>
+      <c r="DE1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_6</t>
+        </is>
+      </c>
+      <c r="DF1" s="1" t="inlineStr">
+        <is>
+          <t>id_player_miss_home_7</t>
+        </is>
+      </c>
+      <c r="DG1" s="1" t="inlineStr">
+        <is>
+          <t>player_name_miss_home_7</t>
+        </is>
+      </c>
+    </row>
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
           <t>v3DAZKP9</t>
         </is>
       </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>AqV0VUgU</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>ronnow frederik</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>W0aQEQqI</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>doekhi danilho</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>U3OLd4oq</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>vogt kevin</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>rmsjwZMd</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>leite diogo</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>drCdG1r7</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>trimmel christopher</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>rFji0QVT</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>kemlein aljoscha</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>nDdRIHZI</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>khedira rani</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>SdlhgTvE</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>skov robert</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>bmevVUsT</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>jeong woo yeong</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>vXXE0beb</t>
+        </is>
+      </c>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>vertessen yorbe</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>Ik1CWJ23</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>hollerbach benedict</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>UwlvfZCm</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>atubolu noah</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr">
+        <is>
+          <t>reFzjZgO</t>
+        </is>
+      </c>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>kubler lukas</t>
+        </is>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>27fpNoQk</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>ginter matthias</t>
+        </is>
+      </c>
+      <c r="AD2" t="inlineStr">
+        <is>
+          <t>Y11H2ibh</t>
+        </is>
+      </c>
+      <c r="AE2" t="inlineStr">
+        <is>
+          <t>lienhart philipp</t>
+        </is>
+      </c>
+      <c r="AF2" t="inlineStr">
+        <is>
+          <t>CYgQyyFL</t>
+        </is>
+      </c>
+      <c r="AG2" t="inlineStr">
+        <is>
+          <t>gunter christian</t>
+        </is>
+      </c>
+      <c r="AH2" t="inlineStr">
+        <is>
+          <t>lbelOv8i</t>
+        </is>
+      </c>
+      <c r="AI2" t="inlineStr">
+        <is>
+          <t>eggestein maximilian</t>
+        </is>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>fcTC5oNR</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>osterhage patrick</t>
+        </is>
+      </c>
+      <c r="AL2" t="inlineStr">
+        <is>
+          <t>WUWvT7l3</t>
+        </is>
+      </c>
+      <c r="AM2" t="inlineStr">
+        <is>
+          <t>doan ritsu</t>
+        </is>
+      </c>
+      <c r="AN2" t="inlineStr">
+        <is>
+          <t>tATOM8P9</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>dinkci eren</t>
+        </is>
+      </c>
+      <c r="AP2" t="inlineStr">
+        <is>
+          <t>jBePSV5m</t>
+        </is>
+      </c>
+      <c r="AQ2" t="inlineStr">
+        <is>
+          <t>grifo vincenzo</t>
+        </is>
+      </c>
+      <c r="AR2" t="inlineStr">
+        <is>
+          <t>4n7MpZtg</t>
+        </is>
+      </c>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>adamu chikwubuike</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>UsQXxleR</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>benes laszlo</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>IRCnlDD8</t>
+        </is>
+      </c>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>haberer janik</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>WtK79lGh</t>
+        </is>
+      </c>
+      <c r="AY2" t="inlineStr">
+        <is>
+          <t>querfeld leopold</t>
+        </is>
+      </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>fVThrU8C</t>
+        </is>
+      </c>
+      <c r="BA2" t="inlineStr">
+        <is>
+          <t>roussillon jerome</t>
+        </is>
+      </c>
+      <c r="BB2" t="inlineStr">
+        <is>
+          <t>8GBj8NFA</t>
+        </is>
+      </c>
+      <c r="BC2" t="inlineStr">
+        <is>
+          <t>schafer andras</t>
+        </is>
+      </c>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>fPL4Y2AK</t>
+        </is>
+      </c>
+      <c r="BE2" t="inlineStr">
+        <is>
+          <t>schwolow alexander</t>
+        </is>
+      </c>
+      <c r="BF2" t="inlineStr">
+        <is>
+          <t>K6XFTXqT</t>
+        </is>
+      </c>
+      <c r="BG2" t="inlineStr">
+        <is>
+          <t>siebatcheu theoson</t>
+        </is>
+      </c>
+      <c r="BH2" t="inlineStr">
+        <is>
+          <t>ObQ0AIvH</t>
+        </is>
+      </c>
+      <c r="BI2" t="inlineStr">
+        <is>
+          <t>skarke tim</t>
+        </is>
+      </c>
+      <c r="BJ2" t="inlineStr">
+        <is>
+          <t>dnpDxpQf</t>
+        </is>
+      </c>
+      <c r="BK2" t="inlineStr">
+        <is>
+          <t>volland kevin</t>
+        </is>
+      </c>
+      <c r="BL2" t="inlineStr">
+        <is>
+          <t>fNPBHb0p</t>
+        </is>
+      </c>
+      <c r="BM2" t="inlineStr">
+        <is>
+          <t>gregoritsch michael</t>
+        </is>
+      </c>
+      <c r="BN2" t="inlineStr">
+        <is>
+          <t>z1kH2LS3</t>
+        </is>
+      </c>
+      <c r="BO2" t="inlineStr">
+        <is>
+          <t>hofler nicolas</t>
+        </is>
+      </c>
+      <c r="BP2" t="inlineStr">
+        <is>
+          <t>WrKkMeeL</t>
+        </is>
+      </c>
+      <c r="BQ2" t="inlineStr">
+        <is>
+          <t>holer lucas</t>
+        </is>
+      </c>
+      <c r="BR2" t="inlineStr">
+        <is>
+          <t>fu2K0qhI</t>
+        </is>
+      </c>
+      <c r="BS2" t="inlineStr">
+        <is>
+          <t>muller florian</t>
+        </is>
+      </c>
+      <c r="BT2" t="inlineStr">
+        <is>
+          <t>W62yKwbK</t>
+        </is>
+      </c>
+      <c r="BU2" t="inlineStr">
+        <is>
+          <t>muslija florent</t>
+        </is>
+      </c>
+      <c r="BV2" t="inlineStr">
+        <is>
+          <t>6PCSjJja</t>
+        </is>
+      </c>
+      <c r="BW2" t="inlineStr">
+        <is>
+          <t>philipp maximilian</t>
+        </is>
+      </c>
+      <c r="BX2" t="inlineStr">
+        <is>
+          <t>21GDpPRq</t>
+        </is>
+      </c>
+      <c r="BY2" t="inlineStr">
+        <is>
+          <t>rosenfelder max</t>
+        </is>
+      </c>
+      <c r="BZ2" t="inlineStr">
+        <is>
+          <t>WCM2C2l0</t>
+        </is>
+      </c>
+      <c r="CA2" t="inlineStr">
+        <is>
+          <t>sildillia kiliann</t>
+        </is>
+      </c>
+      <c r="CB2" t="inlineStr">
+        <is>
+          <t>jFLnII11</t>
+        </is>
+      </c>
+      <c r="CC2" t="inlineStr">
+        <is>
+          <t>weisshaupt noah</t>
+        </is>
+      </c>
+      <c r="CD2" t="inlineStr">
+        <is>
+          <t>WznPyl4k</t>
+        </is>
+      </c>
+      <c r="CE2" t="inlineStr">
+        <is>
+          <t>juranovic josip</t>
+        </is>
+      </c>
+      <c r="CF2" t="inlineStr">
+        <is>
+          <t>WdkYVaj9</t>
+        </is>
+      </c>
+      <c r="CG2" t="inlineStr">
+        <is>
+          <t>prtajin ivan</t>
+        </is>
+      </c>
+      <c r="CH2" t="inlineStr">
+        <is>
+          <t>YJUO3rKf</t>
+        </is>
+      </c>
+      <c r="CI2" t="inlineStr">
+        <is>
+          <t>tousart lucas</t>
+        </is>
+      </c>
+      <c r="CJ2" t="inlineStr">
+        <is>
+          <t>tprC8Q14</t>
+        </is>
+      </c>
+      <c r="CK2" t="inlineStr">
+        <is>
+          <t>ezekwem kimberly</t>
+        </is>
+      </c>
+      <c r="CL2" t="inlineStr">
+        <is>
+          <t>bLZ4JBQc</t>
+        </is>
+      </c>
+      <c r="CM2" t="inlineStr">
+        <is>
+          <t>gulde manuel</t>
+        </is>
+      </c>
+      <c r="CN2" t="inlineStr">
+        <is>
+          <t>tUPHhVGD</t>
+        </is>
+      </c>
+      <c r="CO2" t="inlineStr">
+        <is>
+          <t>kyereh daniel kofi</t>
+        </is>
+      </c>
+      <c r="CP2" t="inlineStr">
+        <is>
+          <t>dOFHqqsj</t>
+        </is>
+      </c>
+      <c r="CQ2" t="inlineStr">
+        <is>
+          <t>makengo jordy</t>
+        </is>
+      </c>
+      <c r="CR2" t="inlineStr">
+        <is>
+          <t>b7FJ7Yb9</t>
+        </is>
+      </c>
+      <c r="CS2" t="inlineStr">
+        <is>
+          <t>rohl merlin</t>
+        </is>
+      </c>
+      <c r="CT2" t="inlineStr">
+        <is>
+          <t>GdruQez1</t>
+        </is>
+      </c>
+      <c r="CU2" t="inlineStr">
+        <is>
+          <t>schmidt kenneth</t>
+        </is>
+      </c>
+      <c r="CV2" t="inlineStr"/>
+      <c r="CW2" t="inlineStr"/>
+      <c r="CX2" t="inlineStr"/>
+      <c r="CY2" t="inlineStr"/>
+      <c r="CZ2" t="inlineStr"/>
+      <c r="DA2" t="inlineStr"/>
+      <c r="DB2" t="inlineStr"/>
+      <c r="DC2" t="inlineStr"/>
+      <c r="DD2" t="inlineStr"/>
+      <c r="DE2" t="inlineStr"/>
+      <c r="DF2" t="inlineStr"/>
+      <c r="DG2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
@@ -441,6 +1495,188 @@
           <t>biQrHC9r</t>
         </is>
       </c>
+      <c r="B3" t="inlineStr"/>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" t="inlineStr"/>
+      <c r="Q3" t="inlineStr"/>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
+      <c r="AE3" t="inlineStr"/>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="inlineStr"/>
+      <c r="AH3" t="inlineStr"/>
+      <c r="AI3" t="inlineStr"/>
+      <c r="AJ3" t="inlineStr"/>
+      <c r="AK3" t="inlineStr"/>
+      <c r="AL3" t="inlineStr"/>
+      <c r="AM3" t="inlineStr"/>
+      <c r="AN3" t="inlineStr"/>
+      <c r="AO3" t="inlineStr"/>
+      <c r="AP3" t="inlineStr"/>
+      <c r="AQ3" t="inlineStr"/>
+      <c r="AR3" t="inlineStr"/>
+      <c r="AS3" t="inlineStr"/>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AU3" t="inlineStr"/>
+      <c r="AV3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr"/>
+      <c r="AX3" t="inlineStr"/>
+      <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr"/>
+      <c r="BA3" t="inlineStr"/>
+      <c r="BB3" t="inlineStr"/>
+      <c r="BC3" t="inlineStr"/>
+      <c r="BD3" t="inlineStr"/>
+      <c r="BE3" t="inlineStr"/>
+      <c r="BF3" t="inlineStr"/>
+      <c r="BG3" t="inlineStr"/>
+      <c r="BH3" t="inlineStr"/>
+      <c r="BI3" t="inlineStr"/>
+      <c r="BJ3" t="inlineStr"/>
+      <c r="BK3" t="inlineStr"/>
+      <c r="BL3" t="inlineStr"/>
+      <c r="BM3" t="inlineStr"/>
+      <c r="BN3" t="inlineStr"/>
+      <c r="BO3" t="inlineStr"/>
+      <c r="BP3" t="inlineStr"/>
+      <c r="BQ3" t="inlineStr"/>
+      <c r="BR3" t="inlineStr"/>
+      <c r="BS3" t="inlineStr"/>
+      <c r="BT3" t="inlineStr"/>
+      <c r="BU3" t="inlineStr"/>
+      <c r="BV3" t="inlineStr"/>
+      <c r="BW3" t="inlineStr"/>
+      <c r="BX3" t="inlineStr"/>
+      <c r="BY3" t="inlineStr"/>
+      <c r="BZ3" t="inlineStr"/>
+      <c r="CA3" t="inlineStr"/>
+      <c r="CB3" t="inlineStr"/>
+      <c r="CC3" t="inlineStr"/>
+      <c r="CD3" t="inlineStr">
+        <is>
+          <t>MwxzFrgA</t>
+        </is>
+      </c>
+      <c r="CE3" t="inlineStr">
+        <is>
+          <t>bernardo</t>
+        </is>
+      </c>
+      <c r="CF3" t="inlineStr">
+        <is>
+          <t>4bt7xopA</t>
+        </is>
+      </c>
+      <c r="CG3" t="inlineStr">
+        <is>
+          <t>tolba mohammed</t>
+        </is>
+      </c>
+      <c r="CH3" t="inlineStr">
+        <is>
+          <t>U7wepPkr</t>
+        </is>
+      </c>
+      <c r="CI3" t="inlineStr">
+        <is>
+          <t>balde aliou</t>
+        </is>
+      </c>
+      <c r="CJ3" t="inlineStr">
+        <is>
+          <t>82ETy0Me</t>
+        </is>
+      </c>
+      <c r="CK3" t="inlineStr">
+        <is>
+          <t>adli amine</t>
+        </is>
+      </c>
+      <c r="CL3" t="inlineStr">
+        <is>
+          <t>zog0NOeM</t>
+        </is>
+      </c>
+      <c r="CM3" t="inlineStr">
+        <is>
+          <t>belocian jeanuel</t>
+        </is>
+      </c>
+      <c r="CN3" t="inlineStr">
+        <is>
+          <t>MoObMvb7</t>
+        </is>
+      </c>
+      <c r="CO3" t="inlineStr">
+        <is>
+          <t>mukiele nordi</t>
+        </is>
+      </c>
+      <c r="CP3" t="inlineStr">
+        <is>
+          <t>xlu6948L</t>
+        </is>
+      </c>
+      <c r="CQ3" t="inlineStr">
+        <is>
+          <t>terrier martin</t>
+        </is>
+      </c>
+      <c r="CR3" t="inlineStr"/>
+      <c r="CS3" t="inlineStr"/>
+      <c r="CT3" t="inlineStr"/>
+      <c r="CU3" t="inlineStr"/>
+      <c r="CV3" t="inlineStr">
+        <is>
+          <t>GE24QNxi</t>
+        </is>
+      </c>
+      <c r="CW3" t="inlineStr">
+        <is>
+          <t>boadu myron</t>
+        </is>
+      </c>
+      <c r="CX3" t="inlineStr">
+        <is>
+          <t>2JfL568j</t>
+        </is>
+      </c>
+      <c r="CY3" t="inlineStr">
+        <is>
+          <t>hofmann philipp</t>
+        </is>
+      </c>
+      <c r="CZ3" t="inlineStr"/>
+      <c r="DA3" t="inlineStr"/>
+      <c r="DB3" t="inlineStr"/>
+      <c r="DC3" t="inlineStr"/>
+      <c r="DD3" t="inlineStr"/>
+      <c r="DE3" t="inlineStr"/>
+      <c r="DF3" t="inlineStr"/>
+      <c r="DG3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
@@ -448,6 +1684,196 @@
           <t>nee3ysec</t>
         </is>
       </c>
+      <c r="B4" t="inlineStr"/>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" t="inlineStr"/>
+      <c r="Q4" t="inlineStr"/>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
+      <c r="AE4" t="inlineStr"/>
+      <c r="AF4" t="inlineStr"/>
+      <c r="AG4" t="inlineStr"/>
+      <c r="AH4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr"/>
+      <c r="AJ4" t="inlineStr"/>
+      <c r="AK4" t="inlineStr"/>
+      <c r="AL4" t="inlineStr"/>
+      <c r="AM4" t="inlineStr"/>
+      <c r="AN4" t="inlineStr"/>
+      <c r="AO4" t="inlineStr"/>
+      <c r="AP4" t="inlineStr"/>
+      <c r="AQ4" t="inlineStr"/>
+      <c r="AR4" t="inlineStr"/>
+      <c r="AS4" t="inlineStr"/>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AU4" t="inlineStr"/>
+      <c r="AV4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr"/>
+      <c r="AX4" t="inlineStr"/>
+      <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr"/>
+      <c r="BA4" t="inlineStr"/>
+      <c r="BB4" t="inlineStr"/>
+      <c r="BC4" t="inlineStr"/>
+      <c r="BD4" t="inlineStr"/>
+      <c r="BE4" t="inlineStr"/>
+      <c r="BF4" t="inlineStr"/>
+      <c r="BG4" t="inlineStr"/>
+      <c r="BH4" t="inlineStr"/>
+      <c r="BI4" t="inlineStr"/>
+      <c r="BJ4" t="inlineStr"/>
+      <c r="BK4" t="inlineStr"/>
+      <c r="BL4" t="inlineStr"/>
+      <c r="BM4" t="inlineStr"/>
+      <c r="BN4" t="inlineStr"/>
+      <c r="BO4" t="inlineStr"/>
+      <c r="BP4" t="inlineStr"/>
+      <c r="BQ4" t="inlineStr"/>
+      <c r="BR4" t="inlineStr"/>
+      <c r="BS4" t="inlineStr"/>
+      <c r="BT4" t="inlineStr"/>
+      <c r="BU4" t="inlineStr"/>
+      <c r="BV4" t="inlineStr"/>
+      <c r="BW4" t="inlineStr"/>
+      <c r="BX4" t="inlineStr"/>
+      <c r="BY4" t="inlineStr"/>
+      <c r="BZ4" t="inlineStr"/>
+      <c r="CA4" t="inlineStr"/>
+      <c r="CB4" t="inlineStr"/>
+      <c r="CC4" t="inlineStr"/>
+      <c r="CD4" t="inlineStr">
+        <is>
+          <t>ru11TuPI</t>
+        </is>
+      </c>
+      <c r="CE4" t="inlineStr">
+        <is>
+          <t>hanche olsen andreas</t>
+        </is>
+      </c>
+      <c r="CF4" t="inlineStr">
+        <is>
+          <t>pIMPjP8B</t>
+        </is>
+      </c>
+      <c r="CG4" t="inlineStr">
+        <is>
+          <t>jenz moritz</t>
+        </is>
+      </c>
+      <c r="CH4" t="inlineStr"/>
+      <c r="CI4" t="inlineStr"/>
+      <c r="CJ4" t="inlineStr">
+        <is>
+          <t>GvIzwgo8</t>
+        </is>
+      </c>
+      <c r="CK4" t="inlineStr">
+        <is>
+          <t>adeyemi karim</t>
+        </is>
+      </c>
+      <c r="CL4" t="inlineStr">
+        <is>
+          <t>b3gqj94D</t>
+        </is>
+      </c>
+      <c r="CM4" t="inlineStr">
+        <is>
+          <t>anton waldemar</t>
+        </is>
+      </c>
+      <c r="CN4" t="inlineStr">
+        <is>
+          <t>jag6GVQG</t>
+        </is>
+      </c>
+      <c r="CO4" t="inlineStr">
+        <is>
+          <t>bensebaini ramy</t>
+        </is>
+      </c>
+      <c r="CP4" t="inlineStr">
+        <is>
+          <t>G8jmgFZE</t>
+        </is>
+      </c>
+      <c r="CQ4" t="inlineStr">
+        <is>
+          <t>duranville julien</t>
+        </is>
+      </c>
+      <c r="CR4" t="inlineStr">
+        <is>
+          <t>xlBg2ttC</t>
+        </is>
+      </c>
+      <c r="CS4" t="inlineStr">
+        <is>
+          <t>kobel gregor</t>
+        </is>
+      </c>
+      <c r="CT4" t="inlineStr">
+        <is>
+          <t>zF5Q2DOk</t>
+        </is>
+      </c>
+      <c r="CU4" t="inlineStr">
+        <is>
+          <t>reyna giovanni</t>
+        </is>
+      </c>
+      <c r="CV4" t="inlineStr"/>
+      <c r="CW4" t="inlineStr"/>
+      <c r="CX4" t="inlineStr"/>
+      <c r="CY4" t="inlineStr"/>
+      <c r="CZ4" t="inlineStr">
+        <is>
+          <t>8nv0ZZYK</t>
+        </is>
+      </c>
+      <c r="DA4" t="inlineStr">
+        <is>
+          <t>ryerson julian</t>
+        </is>
+      </c>
+      <c r="DB4" t="inlineStr">
+        <is>
+          <t>G43Lp4in</t>
+        </is>
+      </c>
+      <c r="DC4" t="inlineStr">
+        <is>
+          <t>sule niklas</t>
+        </is>
+      </c>
+      <c r="DD4" t="inlineStr"/>
+      <c r="DE4" t="inlineStr"/>
+      <c r="DF4" t="inlineStr"/>
+      <c r="DG4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
@@ -455,6 +1881,204 @@
           <t>6HTjFjve</t>
         </is>
       </c>
+      <c r="B5" t="inlineStr"/>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="M5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" t="inlineStr"/>
+      <c r="Q5" t="inlineStr"/>
+      <c r="R5" t="inlineStr"/>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
+      <c r="AE5" t="inlineStr"/>
+      <c r="AF5" t="inlineStr"/>
+      <c r="AG5" t="inlineStr"/>
+      <c r="AH5" t="inlineStr"/>
+      <c r="AI5" t="inlineStr"/>
+      <c r="AJ5" t="inlineStr"/>
+      <c r="AK5" t="inlineStr"/>
+      <c r="AL5" t="inlineStr"/>
+      <c r="AM5" t="inlineStr"/>
+      <c r="AN5" t="inlineStr"/>
+      <c r="AO5" t="inlineStr"/>
+      <c r="AP5" t="inlineStr"/>
+      <c r="AQ5" t="inlineStr"/>
+      <c r="AR5" t="inlineStr"/>
+      <c r="AS5" t="inlineStr"/>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AU5" t="inlineStr"/>
+      <c r="AV5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr"/>
+      <c r="AX5" t="inlineStr"/>
+      <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr"/>
+      <c r="BA5" t="inlineStr"/>
+      <c r="BB5" t="inlineStr"/>
+      <c r="BC5" t="inlineStr"/>
+      <c r="BD5" t="inlineStr"/>
+      <c r="BE5" t="inlineStr"/>
+      <c r="BF5" t="inlineStr"/>
+      <c r="BG5" t="inlineStr"/>
+      <c r="BH5" t="inlineStr"/>
+      <c r="BI5" t="inlineStr"/>
+      <c r="BJ5" t="inlineStr"/>
+      <c r="BK5" t="inlineStr"/>
+      <c r="BL5" t="inlineStr"/>
+      <c r="BM5" t="inlineStr"/>
+      <c r="BN5" t="inlineStr"/>
+      <c r="BO5" t="inlineStr"/>
+      <c r="BP5" t="inlineStr"/>
+      <c r="BQ5" t="inlineStr"/>
+      <c r="BR5" t="inlineStr"/>
+      <c r="BS5" t="inlineStr"/>
+      <c r="BT5" t="inlineStr"/>
+      <c r="BU5" t="inlineStr"/>
+      <c r="BV5" t="inlineStr"/>
+      <c r="BW5" t="inlineStr"/>
+      <c r="BX5" t="inlineStr"/>
+      <c r="BY5" t="inlineStr"/>
+      <c r="BZ5" t="inlineStr"/>
+      <c r="CA5" t="inlineStr"/>
+      <c r="CB5" t="inlineStr"/>
+      <c r="CC5" t="inlineStr"/>
+      <c r="CD5" t="inlineStr">
+        <is>
+          <t>6y5I2kuT</t>
+        </is>
+      </c>
+      <c r="CE5" t="inlineStr">
+        <is>
+          <t>ahlers soren</t>
+        </is>
+      </c>
+      <c r="CF5" t="inlineStr">
+        <is>
+          <t>bHrYrgOk</t>
+        </is>
+      </c>
+      <c r="CG5" t="inlineStr">
+        <is>
+          <t>banks scott</t>
+        </is>
+      </c>
+      <c r="CH5" t="inlineStr">
+        <is>
+          <t>zqXaHPUa</t>
+        </is>
+      </c>
+      <c r="CI5" t="inlineStr">
+        <is>
+          <t>metcalfe connor</t>
+        </is>
+      </c>
+      <c r="CJ5" t="inlineStr">
+        <is>
+          <t>zJ9nejml</t>
+        </is>
+      </c>
+      <c r="CK5" t="inlineStr">
+        <is>
+          <t>boey sacha</t>
+        </is>
+      </c>
+      <c r="CL5" t="inlineStr">
+        <is>
+          <t>dAlY7ECt</t>
+        </is>
+      </c>
+      <c r="CM5" t="inlineStr">
+        <is>
+          <t>buchmann tarek</t>
+        </is>
+      </c>
+      <c r="CN5" t="inlineStr">
+        <is>
+          <t>4ULsVw9c</t>
+        </is>
+      </c>
+      <c r="CO5" t="inlineStr">
+        <is>
+          <t>ito hiroki</t>
+        </is>
+      </c>
+      <c r="CP5" t="inlineStr">
+        <is>
+          <t>noANPQx4</t>
+        </is>
+      </c>
+      <c r="CQ5" t="inlineStr">
+        <is>
+          <t>pavlovic aleksandar</t>
+        </is>
+      </c>
+      <c r="CR5" t="inlineStr">
+        <is>
+          <t>SfawK0Y3</t>
+        </is>
+      </c>
+      <c r="CS5" t="inlineStr">
+        <is>
+          <t>stanisic josip</t>
+        </is>
+      </c>
+      <c r="CT5" t="inlineStr"/>
+      <c r="CU5" t="inlineStr"/>
+      <c r="CV5" t="inlineStr">
+        <is>
+          <t>rcSN3FVD</t>
+        </is>
+      </c>
+      <c r="CW5" t="inlineStr">
+        <is>
+          <t>saad elias</t>
+        </is>
+      </c>
+      <c r="CX5" t="inlineStr">
+        <is>
+          <t>zXOjivLH</t>
+        </is>
+      </c>
+      <c r="CY5" t="inlineStr">
+        <is>
+          <t>treu philipp</t>
+        </is>
+      </c>
+      <c r="CZ5" t="inlineStr"/>
+      <c r="DA5" t="inlineStr"/>
+      <c r="DB5" t="inlineStr"/>
+      <c r="DC5" t="inlineStr"/>
+      <c r="DD5" t="inlineStr">
+        <is>
+          <t>nNQpJoz5</t>
+        </is>
+      </c>
+      <c r="DE5" t="inlineStr">
+        <is>
+          <t>voll ben alexander</t>
+        </is>
+      </c>
+      <c r="DF5" t="inlineStr"/>
+      <c r="DG5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
@@ -462,6 +2086,196 @@
           <t>YmumZjET</t>
         </is>
       </c>
+      <c r="B6" t="inlineStr"/>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr"/>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" t="inlineStr"/>
+      <c r="Q6" t="inlineStr"/>
+      <c r="R6" t="inlineStr"/>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
+      <c r="AE6" t="inlineStr"/>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="inlineStr"/>
+      <c r="AH6" t="inlineStr"/>
+      <c r="AI6" t="inlineStr"/>
+      <c r="AJ6" t="inlineStr"/>
+      <c r="AK6" t="inlineStr"/>
+      <c r="AL6" t="inlineStr"/>
+      <c r="AM6" t="inlineStr"/>
+      <c r="AN6" t="inlineStr"/>
+      <c r="AO6" t="inlineStr"/>
+      <c r="AP6" t="inlineStr"/>
+      <c r="AQ6" t="inlineStr"/>
+      <c r="AR6" t="inlineStr"/>
+      <c r="AS6" t="inlineStr"/>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AU6" t="inlineStr"/>
+      <c r="AV6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr"/>
+      <c r="AX6" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr"/>
+      <c r="BA6" t="inlineStr"/>
+      <c r="BB6" t="inlineStr"/>
+      <c r="BC6" t="inlineStr"/>
+      <c r="BD6" t="inlineStr"/>
+      <c r="BE6" t="inlineStr"/>
+      <c r="BF6" t="inlineStr"/>
+      <c r="BG6" t="inlineStr"/>
+      <c r="BH6" t="inlineStr"/>
+      <c r="BI6" t="inlineStr"/>
+      <c r="BJ6" t="inlineStr"/>
+      <c r="BK6" t="inlineStr"/>
+      <c r="BL6" t="inlineStr"/>
+      <c r="BM6" t="inlineStr"/>
+      <c r="BN6" t="inlineStr"/>
+      <c r="BO6" t="inlineStr"/>
+      <c r="BP6" t="inlineStr"/>
+      <c r="BQ6" t="inlineStr"/>
+      <c r="BR6" t="inlineStr"/>
+      <c r="BS6" t="inlineStr"/>
+      <c r="BT6" t="inlineStr"/>
+      <c r="BU6" t="inlineStr"/>
+      <c r="BV6" t="inlineStr"/>
+      <c r="BW6" t="inlineStr"/>
+      <c r="BX6" t="inlineStr"/>
+      <c r="BY6" t="inlineStr"/>
+      <c r="BZ6" t="inlineStr"/>
+      <c r="CA6" t="inlineStr"/>
+      <c r="CB6" t="inlineStr"/>
+      <c r="CC6" t="inlineStr"/>
+      <c r="CD6" t="inlineStr">
+        <is>
+          <t>hCB1UCHG</t>
+        </is>
+      </c>
+      <c r="CE6" t="inlineStr">
+        <is>
+          <t>grull marco</t>
+        </is>
+      </c>
+      <c r="CF6" t="inlineStr">
+        <is>
+          <t>4MB78NvI</t>
+        </is>
+      </c>
+      <c r="CG6" t="inlineStr">
+        <is>
+          <t>keita naby</t>
+        </is>
+      </c>
+      <c r="CH6" t="inlineStr">
+        <is>
+          <t>tYnkajw9</t>
+        </is>
+      </c>
+      <c r="CI6" t="inlineStr">
+        <is>
+          <t>weiser mitchell</t>
+        </is>
+      </c>
+      <c r="CJ6" t="inlineStr">
+        <is>
+          <t>4lxZ6TzS</t>
+        </is>
+      </c>
+      <c r="CK6" t="inlineStr">
+        <is>
+          <t>johansson carl</t>
+        </is>
+      </c>
+      <c r="CL6" t="inlineStr">
+        <is>
+          <t>jaQQ0fMu</t>
+        </is>
+      </c>
+      <c r="CM6" t="inlineStr">
+        <is>
+          <t>kelati andu yobel</t>
+        </is>
+      </c>
+      <c r="CN6" t="inlineStr">
+        <is>
+          <t>O4aDKvnH</t>
+        </is>
+      </c>
+      <c r="CO6" t="inlineStr">
+        <is>
+          <t>kleine bekel colin noah</t>
+        </is>
+      </c>
+      <c r="CP6" t="inlineStr">
+        <is>
+          <t>0Ah8TRF1</t>
+        </is>
+      </c>
+      <c r="CQ6" t="inlineStr">
+        <is>
+          <t>bernhardsson alexander</t>
+        </is>
+      </c>
+      <c r="CR6" t="inlineStr">
+        <is>
+          <t>EDemoJW7</t>
+        </is>
+      </c>
+      <c r="CS6" t="inlineStr">
+        <is>
+          <t>holtby lewis</t>
+        </is>
+      </c>
+      <c r="CT6" t="inlineStr"/>
+      <c r="CU6" t="inlineStr"/>
+      <c r="CV6" t="inlineStr">
+        <is>
+          <t>WlEZExcF</t>
+        </is>
+      </c>
+      <c r="CW6" t="inlineStr">
+        <is>
+          <t>alvero skelly</t>
+        </is>
+      </c>
+      <c r="CX6" t="inlineStr">
+        <is>
+          <t>xQzNNXkj</t>
+        </is>
+      </c>
+      <c r="CY6" t="inlineStr">
+        <is>
+          <t>stark niklas</t>
+        </is>
+      </c>
+      <c r="CZ6" t="inlineStr"/>
+      <c r="DA6" t="inlineStr"/>
+      <c r="DB6" t="inlineStr"/>
+      <c r="DC6" t="inlineStr"/>
+      <c r="DD6" t="inlineStr"/>
+      <c r="DE6" t="inlineStr"/>
+      <c r="DF6" t="inlineStr"/>
+      <c r="DG6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
@@ -469,6 +2283,212 @@
           <t>j5mWxZE4</t>
         </is>
       </c>
+      <c r="B7" t="inlineStr"/>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr"/>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" t="inlineStr"/>
+      <c r="Q7" t="inlineStr"/>
+      <c r="R7" t="inlineStr"/>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
+      <c r="AE7" t="inlineStr"/>
+      <c r="AF7" t="inlineStr"/>
+      <c r="AG7" t="inlineStr"/>
+      <c r="AH7" t="inlineStr"/>
+      <c r="AI7" t="inlineStr"/>
+      <c r="AJ7" t="inlineStr"/>
+      <c r="AK7" t="inlineStr"/>
+      <c r="AL7" t="inlineStr"/>
+      <c r="AM7" t="inlineStr"/>
+      <c r="AN7" t="inlineStr"/>
+      <c r="AO7" t="inlineStr"/>
+      <c r="AP7" t="inlineStr"/>
+      <c r="AQ7" t="inlineStr"/>
+      <c r="AR7" t="inlineStr"/>
+      <c r="AS7" t="inlineStr"/>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AU7" t="inlineStr"/>
+      <c r="AV7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr"/>
+      <c r="AX7" t="inlineStr"/>
+      <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr"/>
+      <c r="BA7" t="inlineStr"/>
+      <c r="BB7" t="inlineStr"/>
+      <c r="BC7" t="inlineStr"/>
+      <c r="BD7" t="inlineStr"/>
+      <c r="BE7" t="inlineStr"/>
+      <c r="BF7" t="inlineStr"/>
+      <c r="BG7" t="inlineStr"/>
+      <c r="BH7" t="inlineStr"/>
+      <c r="BI7" t="inlineStr"/>
+      <c r="BJ7" t="inlineStr"/>
+      <c r="BK7" t="inlineStr"/>
+      <c r="BL7" t="inlineStr"/>
+      <c r="BM7" t="inlineStr"/>
+      <c r="BN7" t="inlineStr"/>
+      <c r="BO7" t="inlineStr"/>
+      <c r="BP7" t="inlineStr"/>
+      <c r="BQ7" t="inlineStr"/>
+      <c r="BR7" t="inlineStr"/>
+      <c r="BS7" t="inlineStr"/>
+      <c r="BT7" t="inlineStr"/>
+      <c r="BU7" t="inlineStr"/>
+      <c r="BV7" t="inlineStr"/>
+      <c r="BW7" t="inlineStr"/>
+      <c r="BX7" t="inlineStr"/>
+      <c r="BY7" t="inlineStr"/>
+      <c r="BZ7" t="inlineStr"/>
+      <c r="CA7" t="inlineStr"/>
+      <c r="CB7" t="inlineStr"/>
+      <c r="CC7" t="inlineStr"/>
+      <c r="CD7" t="inlineStr">
+        <is>
+          <t>6X0C61vo</t>
+        </is>
+      </c>
+      <c r="CE7" t="inlineStr">
+        <is>
+          <t>lukeba castello</t>
+        </is>
+      </c>
+      <c r="CF7" t="inlineStr">
+        <is>
+          <t>2XVqEh8k</t>
+        </is>
+      </c>
+      <c r="CG7" t="inlineStr">
+        <is>
+          <t>raum david</t>
+        </is>
+      </c>
+      <c r="CH7" t="inlineStr">
+        <is>
+          <t>M1bcCLIU</t>
+        </is>
+      </c>
+      <c r="CI7" t="inlineStr">
+        <is>
+          <t>schlager xaver</t>
+        </is>
+      </c>
+      <c r="CJ7" t="inlineStr">
+        <is>
+          <t>ltDOVSGt</t>
+        </is>
+      </c>
+      <c r="CK7" t="inlineStr">
+        <is>
+          <t>borges sanches yvandro</t>
+        </is>
+      </c>
+      <c r="CL7" t="inlineStr">
+        <is>
+          <t>fZO9OHIM</t>
+        </is>
+      </c>
+      <c r="CM7" t="inlineStr">
+        <is>
+          <t>elvedi nico</t>
+        </is>
+      </c>
+      <c r="CN7" t="inlineStr">
+        <is>
+          <t>bDOAkNvH</t>
+        </is>
+      </c>
+      <c r="CO7" t="inlineStr">
+        <is>
+          <t>ngoumou nathan</t>
+        </is>
+      </c>
+      <c r="CP7" t="inlineStr">
+        <is>
+          <t>MyyplBl4</t>
+        </is>
+      </c>
+      <c r="CQ7" t="inlineStr">
+        <is>
+          <t>olschowsky jan</t>
+        </is>
+      </c>
+      <c r="CR7" t="inlineStr">
+        <is>
+          <t>YZUjjz4A</t>
+        </is>
+      </c>
+      <c r="CS7" t="inlineStr">
+        <is>
+          <t>netz luca</t>
+        </is>
+      </c>
+      <c r="CT7" t="inlineStr">
+        <is>
+          <t>IwP3NZs5</t>
+        </is>
+      </c>
+      <c r="CU7" t="inlineStr">
+        <is>
+          <t>omlin jonas</t>
+        </is>
+      </c>
+      <c r="CV7" t="inlineStr">
+        <is>
+          <t>noo0L9zk</t>
+        </is>
+      </c>
+      <c r="CW7" t="inlineStr">
+        <is>
+          <t>simons xavi</t>
+        </is>
+      </c>
+      <c r="CX7" t="inlineStr"/>
+      <c r="CY7" t="inlineStr"/>
+      <c r="CZ7" t="inlineStr">
+        <is>
+          <t>0rfLpu2t</t>
+        </is>
+      </c>
+      <c r="DA7" t="inlineStr">
+        <is>
+          <t>plea alassane</t>
+        </is>
+      </c>
+      <c r="DB7" t="inlineStr">
+        <is>
+          <t>ruMn6c8t</t>
+        </is>
+      </c>
+      <c r="DC7" t="inlineStr">
+        <is>
+          <t>walde simon</t>
+        </is>
+      </c>
+      <c r="DD7" t="inlineStr"/>
+      <c r="DE7" t="inlineStr"/>
+      <c r="DF7" t="inlineStr"/>
+      <c r="DG7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
@@ -476,6 +2496,204 @@
           <t>UJQITUyi</t>
         </is>
       </c>
+      <c r="B8" t="inlineStr"/>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr"/>
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" t="inlineStr"/>
+      <c r="Q8" t="inlineStr"/>
+      <c r="R8" t="inlineStr"/>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
+      <c r="AE8" t="inlineStr"/>
+      <c r="AF8" t="inlineStr"/>
+      <c r="AG8" t="inlineStr"/>
+      <c r="AH8" t="inlineStr"/>
+      <c r="AI8" t="inlineStr"/>
+      <c r="AJ8" t="inlineStr"/>
+      <c r="AK8" t="inlineStr"/>
+      <c r="AL8" t="inlineStr"/>
+      <c r="AM8" t="inlineStr"/>
+      <c r="AN8" t="inlineStr"/>
+      <c r="AO8" t="inlineStr"/>
+      <c r="AP8" t="inlineStr"/>
+      <c r="AQ8" t="inlineStr"/>
+      <c r="AR8" t="inlineStr"/>
+      <c r="AS8" t="inlineStr"/>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AU8" t="inlineStr"/>
+      <c r="AV8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr"/>
+      <c r="AX8" t="inlineStr"/>
+      <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr"/>
+      <c r="BA8" t="inlineStr"/>
+      <c r="BB8" t="inlineStr"/>
+      <c r="BC8" t="inlineStr"/>
+      <c r="BD8" t="inlineStr"/>
+      <c r="BE8" t="inlineStr"/>
+      <c r="BF8" t="inlineStr"/>
+      <c r="BG8" t="inlineStr"/>
+      <c r="BH8" t="inlineStr"/>
+      <c r="BI8" t="inlineStr"/>
+      <c r="BJ8" t="inlineStr"/>
+      <c r="BK8" t="inlineStr"/>
+      <c r="BL8" t="inlineStr"/>
+      <c r="BM8" t="inlineStr"/>
+      <c r="BN8" t="inlineStr"/>
+      <c r="BO8" t="inlineStr"/>
+      <c r="BP8" t="inlineStr"/>
+      <c r="BQ8" t="inlineStr"/>
+      <c r="BR8" t="inlineStr"/>
+      <c r="BS8" t="inlineStr"/>
+      <c r="BT8" t="inlineStr"/>
+      <c r="BU8" t="inlineStr"/>
+      <c r="BV8" t="inlineStr"/>
+      <c r="BW8" t="inlineStr"/>
+      <c r="BX8" t="inlineStr"/>
+      <c r="BY8" t="inlineStr"/>
+      <c r="BZ8" t="inlineStr"/>
+      <c r="CA8" t="inlineStr"/>
+      <c r="CB8" t="inlineStr"/>
+      <c r="CC8" t="inlineStr"/>
+      <c r="CD8" t="inlineStr">
+        <is>
+          <t>OKcwlyhN</t>
+        </is>
+      </c>
+      <c r="CE8" t="inlineStr">
+        <is>
+          <t>framberger raphael</t>
+        </is>
+      </c>
+      <c r="CF8" t="inlineStr">
+        <is>
+          <t>x8uj789H</t>
+        </is>
+      </c>
+      <c r="CG8" t="inlineStr">
+        <is>
+          <t>gumny robert</t>
+        </is>
+      </c>
+      <c r="CH8" t="inlineStr">
+        <is>
+          <t>YJdpejUK</t>
+        </is>
+      </c>
+      <c r="CI8" t="inlineStr">
+        <is>
+          <t>jensen fredrik</t>
+        </is>
+      </c>
+      <c r="CJ8" t="inlineStr">
+        <is>
+          <t>tbJx15yJ</t>
+        </is>
+      </c>
+      <c r="CK8" t="inlineStr">
+        <is>
+          <t>bebou ihlas</t>
+        </is>
+      </c>
+      <c r="CL8" t="inlineStr">
+        <is>
+          <t>nBbGuPN8</t>
+        </is>
+      </c>
+      <c r="CM8" t="inlineStr">
+        <is>
+          <t>kabak ozan</t>
+        </is>
+      </c>
+      <c r="CN8" t="inlineStr">
+        <is>
+          <t>GOTDkA9I</t>
+        </is>
+      </c>
+      <c r="CO8" t="inlineStr">
+        <is>
+          <t>promel grischa</t>
+        </is>
+      </c>
+      <c r="CP8" t="inlineStr">
+        <is>
+          <t>OrIOjLpG</t>
+        </is>
+      </c>
+      <c r="CQ8" t="inlineStr">
+        <is>
+          <t>becker finn ole</t>
+        </is>
+      </c>
+      <c r="CR8" t="inlineStr"/>
+      <c r="CS8" t="inlineStr"/>
+      <c r="CT8" t="inlineStr"/>
+      <c r="CU8" t="inlineStr"/>
+      <c r="CV8" t="inlineStr">
+        <is>
+          <t>KC0NKT7S</t>
+        </is>
+      </c>
+      <c r="CW8" t="inlineStr">
+        <is>
+          <t>oxford reece</t>
+        </is>
+      </c>
+      <c r="CX8" t="inlineStr">
+        <is>
+          <t>dEsUd870</t>
+        </is>
+      </c>
+      <c r="CY8" t="inlineStr">
+        <is>
+          <t>rexhbecaj elvis</t>
+        </is>
+      </c>
+      <c r="CZ8" t="inlineStr"/>
+      <c r="DA8" t="inlineStr"/>
+      <c r="DB8" t="inlineStr"/>
+      <c r="DC8" t="inlineStr"/>
+      <c r="DD8" t="inlineStr">
+        <is>
+          <t>U7XUxOei</t>
+        </is>
+      </c>
+      <c r="DE8" t="inlineStr">
+        <is>
+          <t>vargas ruben</t>
+        </is>
+      </c>
+      <c r="DF8" t="inlineStr">
+        <is>
+          <t>6iPxFKjf</t>
+        </is>
+      </c>
+      <c r="DG8" t="inlineStr">
+        <is>
+          <t>pedersen mads</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
@@ -483,6 +2701,204 @@
           <t>UkaNveph</t>
         </is>
       </c>
+      <c r="B9" t="inlineStr"/>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" t="inlineStr"/>
+      <c r="Q9" t="inlineStr"/>
+      <c r="R9" t="inlineStr"/>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
+      <c r="AE9" t="inlineStr"/>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="inlineStr"/>
+      <c r="AH9" t="inlineStr"/>
+      <c r="AI9" t="inlineStr"/>
+      <c r="AJ9" t="inlineStr"/>
+      <c r="AK9" t="inlineStr"/>
+      <c r="AL9" t="inlineStr"/>
+      <c r="AM9" t="inlineStr"/>
+      <c r="AN9" t="inlineStr"/>
+      <c r="AO9" t="inlineStr"/>
+      <c r="AP9" t="inlineStr"/>
+      <c r="AQ9" t="inlineStr"/>
+      <c r="AR9" t="inlineStr"/>
+      <c r="AS9" t="inlineStr"/>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AU9" t="inlineStr"/>
+      <c r="AV9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr"/>
+      <c r="AX9" t="inlineStr"/>
+      <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr"/>
+      <c r="BA9" t="inlineStr"/>
+      <c r="BB9" t="inlineStr"/>
+      <c r="BC9" t="inlineStr"/>
+      <c r="BD9" t="inlineStr"/>
+      <c r="BE9" t="inlineStr"/>
+      <c r="BF9" t="inlineStr"/>
+      <c r="BG9" t="inlineStr"/>
+      <c r="BH9" t="inlineStr"/>
+      <c r="BI9" t="inlineStr"/>
+      <c r="BJ9" t="inlineStr"/>
+      <c r="BK9" t="inlineStr"/>
+      <c r="BL9" t="inlineStr"/>
+      <c r="BM9" t="inlineStr"/>
+      <c r="BN9" t="inlineStr"/>
+      <c r="BO9" t="inlineStr"/>
+      <c r="BP9" t="inlineStr"/>
+      <c r="BQ9" t="inlineStr"/>
+      <c r="BR9" t="inlineStr"/>
+      <c r="BS9" t="inlineStr"/>
+      <c r="BT9" t="inlineStr"/>
+      <c r="BU9" t="inlineStr"/>
+      <c r="BV9" t="inlineStr"/>
+      <c r="BW9" t="inlineStr"/>
+      <c r="BX9" t="inlineStr"/>
+      <c r="BY9" t="inlineStr"/>
+      <c r="BZ9" t="inlineStr"/>
+      <c r="CA9" t="inlineStr"/>
+      <c r="CB9" t="inlineStr"/>
+      <c r="CC9" t="inlineStr"/>
+      <c r="CD9" t="inlineStr">
+        <is>
+          <t>UTtpcjym</t>
+        </is>
+      </c>
+      <c r="CE9" t="inlineStr">
+        <is>
+          <t>leweling jamie</t>
+        </is>
+      </c>
+      <c r="CF9" t="inlineStr">
+        <is>
+          <t>ja18uZOO</t>
+        </is>
+      </c>
+      <c r="CG9" t="inlineStr">
+        <is>
+          <t>nartey nikolas</t>
+        </is>
+      </c>
+      <c r="CH9" t="inlineStr">
+        <is>
+          <t>YFNUTMWH</t>
+        </is>
+      </c>
+      <c r="CI9" t="inlineStr">
+        <is>
+          <t>raimund luca</t>
+        </is>
+      </c>
+      <c r="CJ9" t="inlineStr">
+        <is>
+          <t>WWSwmP1d</t>
+        </is>
+      </c>
+      <c r="CK9" t="inlineStr">
+        <is>
+          <t>hojlund oscar</t>
+        </is>
+      </c>
+      <c r="CL9" t="inlineStr">
+        <is>
+          <t>Ii8pjsY2</t>
+        </is>
+      </c>
+      <c r="CM9" t="inlineStr">
+        <is>
+          <t>kristensen rasmus</t>
+        </is>
+      </c>
+      <c r="CN9" t="inlineStr">
+        <is>
+          <t>4MlIIRDU</t>
+        </is>
+      </c>
+      <c r="CO9" t="inlineStr">
+        <is>
+          <t>loune mehdi</t>
+        </is>
+      </c>
+      <c r="CP9" t="inlineStr">
+        <is>
+          <t>pYy1apYK</t>
+        </is>
+      </c>
+      <c r="CQ9" t="inlineStr">
+        <is>
+          <t>wenig marcel</t>
+        </is>
+      </c>
+      <c r="CR9" t="inlineStr"/>
+      <c r="CS9" t="inlineStr"/>
+      <c r="CT9" t="inlineStr"/>
+      <c r="CU9" t="inlineStr"/>
+      <c r="CV9" t="inlineStr">
+        <is>
+          <t>j1IjJkHI</t>
+        </is>
+      </c>
+      <c r="CW9" t="inlineStr">
+        <is>
+          <t>zagadou dan axel</t>
+        </is>
+      </c>
+      <c r="CX9" t="inlineStr">
+        <is>
+          <t>tSVfwjYd</t>
+        </is>
+      </c>
+      <c r="CY9" t="inlineStr">
+        <is>
+          <t>diehl justin</t>
+        </is>
+      </c>
+      <c r="CZ9" t="inlineStr"/>
+      <c r="DA9" t="inlineStr"/>
+      <c r="DB9" t="inlineStr"/>
+      <c r="DC9" t="inlineStr"/>
+      <c r="DD9" t="inlineStr">
+        <is>
+          <t>vVKqrtep</t>
+        </is>
+      </c>
+      <c r="DE9" t="inlineStr">
+        <is>
+          <t>stergiou leonidas</t>
+        </is>
+      </c>
+      <c r="DF9" t="inlineStr">
+        <is>
+          <t>tUHAdtMH</t>
+        </is>
+      </c>
+      <c r="DG9" t="inlineStr">
+        <is>
+          <t>undav deniz</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
@@ -490,6 +2906,1023 @@
           <t>xMovyDqH</t>
         </is>
       </c>
+      <c r="B10" t="inlineStr"/>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
+      <c r="N10" t="inlineStr"/>
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" t="inlineStr"/>
+      <c r="Q10" t="inlineStr"/>
+      <c r="R10" t="inlineStr"/>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
+      <c r="AE10" t="inlineStr"/>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="inlineStr"/>
+      <c r="AH10" t="inlineStr"/>
+      <c r="AI10" t="inlineStr"/>
+      <c r="AJ10" t="inlineStr"/>
+      <c r="AK10" t="inlineStr"/>
+      <c r="AL10" t="inlineStr"/>
+      <c r="AM10" t="inlineStr"/>
+      <c r="AN10" t="inlineStr"/>
+      <c r="AO10" t="inlineStr"/>
+      <c r="AP10" t="inlineStr"/>
+      <c r="AQ10" t="inlineStr"/>
+      <c r="AR10" t="inlineStr"/>
+      <c r="AS10" t="inlineStr"/>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AU10" t="inlineStr"/>
+      <c r="AV10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr"/>
+      <c r="AX10" t="inlineStr"/>
+      <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr"/>
+      <c r="BA10" t="inlineStr"/>
+      <c r="BB10" t="inlineStr"/>
+      <c r="BC10" t="inlineStr"/>
+      <c r="BD10" t="inlineStr"/>
+      <c r="BE10" t="inlineStr"/>
+      <c r="BF10" t="inlineStr"/>
+      <c r="BG10" t="inlineStr"/>
+      <c r="BH10" t="inlineStr"/>
+      <c r="BI10" t="inlineStr"/>
+      <c r="BJ10" t="inlineStr"/>
+      <c r="BK10" t="inlineStr"/>
+      <c r="BL10" t="inlineStr"/>
+      <c r="BM10" t="inlineStr"/>
+      <c r="BN10" t="inlineStr"/>
+      <c r="BO10" t="inlineStr"/>
+      <c r="BP10" t="inlineStr"/>
+      <c r="BQ10" t="inlineStr"/>
+      <c r="BR10" t="inlineStr"/>
+      <c r="BS10" t="inlineStr"/>
+      <c r="BT10" t="inlineStr"/>
+      <c r="BU10" t="inlineStr"/>
+      <c r="BV10" t="inlineStr"/>
+      <c r="BW10" t="inlineStr"/>
+      <c r="BX10" t="inlineStr"/>
+      <c r="BY10" t="inlineStr"/>
+      <c r="BZ10" t="inlineStr"/>
+      <c r="CA10" t="inlineStr"/>
+      <c r="CB10" t="inlineStr"/>
+      <c r="CC10" t="inlineStr"/>
+      <c r="CD10" t="inlineStr">
+        <is>
+          <t>vTDGEfNG</t>
+        </is>
+      </c>
+      <c r="CE10" t="inlineStr">
+        <is>
+          <t>keller thomas</t>
+        </is>
+      </c>
+      <c r="CF10" t="inlineStr">
+        <is>
+          <t>80wjP4AN</t>
+        </is>
+      </c>
+      <c r="CG10" t="inlineStr">
+        <is>
+          <t>niehues julian</t>
+        </is>
+      </c>
+      <c r="CH10" t="inlineStr">
+        <is>
+          <t>nuLsDXY4</t>
+        </is>
+      </c>
+      <c r="CI10" t="inlineStr">
+        <is>
+          <t>janes luka</t>
+        </is>
+      </c>
+      <c r="CJ10" t="inlineStr">
+        <is>
+          <t>pleKaexP</t>
+        </is>
+      </c>
+      <c r="CK10" t="inlineStr">
+        <is>
+          <t>bialek bartosz</t>
+        </is>
+      </c>
+      <c r="CL10" t="inlineStr">
+        <is>
+          <t>6D2Vm8M8</t>
+        </is>
+      </c>
+      <c r="CM10" t="inlineStr">
+        <is>
+          <t>nmecha lukas</t>
+        </is>
+      </c>
+      <c r="CN10" t="inlineStr">
+        <is>
+          <t>OrlbhXJo</t>
+        </is>
+      </c>
+      <c r="CO10" t="inlineStr">
+        <is>
+          <t>rogerio</t>
+        </is>
+      </c>
+      <c r="CP10" t="inlineStr">
+        <is>
+          <t>z58rzyyp</t>
+        </is>
+      </c>
+      <c r="CQ10" t="inlineStr">
+        <is>
+          <t>bornauw sebastiaan</t>
+        </is>
+      </c>
+      <c r="CR10" t="inlineStr">
+        <is>
+          <t>444Jw1Mr</t>
+        </is>
+      </c>
+      <c r="CS10" t="inlineStr">
+        <is>
+          <t>majer lovro</t>
+        </is>
+      </c>
+      <c r="CT10" t="inlineStr">
+        <is>
+          <t>lIg2Sr9i</t>
+        </is>
+      </c>
+      <c r="CU10" t="inlineStr">
+        <is>
+          <t>paredes kevin</t>
+        </is>
+      </c>
+      <c r="CV10" t="inlineStr"/>
+      <c r="CW10" t="inlineStr"/>
+      <c r="CX10" t="inlineStr"/>
+      <c r="CY10" t="inlineStr"/>
+      <c r="CZ10" t="inlineStr">
+        <is>
+          <t>z522mgfh</t>
+        </is>
+      </c>
+      <c r="DA10" t="inlineStr">
+        <is>
+          <t>svanberg mattias</t>
+        </is>
+      </c>
+      <c r="DB10" t="inlineStr">
+        <is>
+          <t>EqNGX6pE</t>
+        </is>
+      </c>
+      <c r="DC10" t="inlineStr">
+        <is>
+          <t>vranckx aster</t>
+        </is>
+      </c>
+      <c r="DD10" t="inlineStr"/>
+      <c r="DE10" t="inlineStr"/>
+      <c r="DF10" t="inlineStr"/>
+      <c r="DG10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>EuQnZBVQ</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr"/>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr"/>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" t="inlineStr"/>
+      <c r="Q11" t="inlineStr"/>
+      <c r="R11" t="inlineStr"/>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
+      <c r="AE11" t="inlineStr"/>
+      <c r="AF11" t="inlineStr"/>
+      <c r="AG11" t="inlineStr"/>
+      <c r="AH11" t="inlineStr"/>
+      <c r="AI11" t="inlineStr"/>
+      <c r="AJ11" t="inlineStr"/>
+      <c r="AK11" t="inlineStr"/>
+      <c r="AL11" t="inlineStr"/>
+      <c r="AM11" t="inlineStr"/>
+      <c r="AN11" t="inlineStr"/>
+      <c r="AO11" t="inlineStr"/>
+      <c r="AP11" t="inlineStr"/>
+      <c r="AQ11" t="inlineStr"/>
+      <c r="AR11" t="inlineStr"/>
+      <c r="AS11" t="inlineStr"/>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AU11" t="inlineStr"/>
+      <c r="AV11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr"/>
+      <c r="AX11" t="inlineStr"/>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr"/>
+      <c r="BA11" t="inlineStr"/>
+      <c r="BB11" t="inlineStr"/>
+      <c r="BC11" t="inlineStr"/>
+      <c r="BD11" t="inlineStr"/>
+      <c r="BE11" t="inlineStr"/>
+      <c r="BF11" t="inlineStr"/>
+      <c r="BG11" t="inlineStr"/>
+      <c r="BH11" t="inlineStr"/>
+      <c r="BI11" t="inlineStr"/>
+      <c r="BJ11" t="inlineStr"/>
+      <c r="BK11" t="inlineStr"/>
+      <c r="BL11" t="inlineStr"/>
+      <c r="BM11" t="inlineStr"/>
+      <c r="BN11" t="inlineStr"/>
+      <c r="BO11" t="inlineStr"/>
+      <c r="BP11" t="inlineStr"/>
+      <c r="BQ11" t="inlineStr"/>
+      <c r="BR11" t="inlineStr"/>
+      <c r="BS11" t="inlineStr"/>
+      <c r="BT11" t="inlineStr"/>
+      <c r="BU11" t="inlineStr"/>
+      <c r="BV11" t="inlineStr"/>
+      <c r="BW11" t="inlineStr"/>
+      <c r="BX11" t="inlineStr"/>
+      <c r="BY11" t="inlineStr"/>
+      <c r="BZ11" t="inlineStr"/>
+      <c r="CA11" t="inlineStr"/>
+      <c r="CB11" t="inlineStr"/>
+      <c r="CC11" t="inlineStr"/>
+      <c r="CD11" t="inlineStr"/>
+      <c r="CE11" t="inlineStr"/>
+      <c r="CF11" t="inlineStr"/>
+      <c r="CG11" t="inlineStr"/>
+      <c r="CH11" t="inlineStr"/>
+      <c r="CI11" t="inlineStr"/>
+      <c r="CJ11" t="inlineStr"/>
+      <c r="CK11" t="inlineStr"/>
+      <c r="CL11" t="inlineStr"/>
+      <c r="CM11" t="inlineStr"/>
+      <c r="CN11" t="inlineStr"/>
+      <c r="CO11" t="inlineStr"/>
+      <c r="CP11" t="inlineStr"/>
+      <c r="CQ11" t="inlineStr"/>
+      <c r="CR11" t="inlineStr"/>
+      <c r="CS11" t="inlineStr"/>
+      <c r="CT11" t="inlineStr"/>
+      <c r="CU11" t="inlineStr"/>
+      <c r="CV11" t="inlineStr"/>
+      <c r="CW11" t="inlineStr"/>
+      <c r="CX11" t="inlineStr"/>
+      <c r="CY11" t="inlineStr"/>
+      <c r="CZ11" t="inlineStr"/>
+      <c r="DA11" t="inlineStr"/>
+      <c r="DB11" t="inlineStr"/>
+      <c r="DC11" t="inlineStr"/>
+      <c r="DD11" t="inlineStr"/>
+      <c r="DE11" t="inlineStr"/>
+      <c r="DF11" t="inlineStr"/>
+      <c r="DG11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>2qNaDU87</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr"/>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr"/>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" t="inlineStr"/>
+      <c r="Q12" t="inlineStr"/>
+      <c r="R12" t="inlineStr"/>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
+      <c r="AE12" t="inlineStr"/>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="inlineStr"/>
+      <c r="AH12" t="inlineStr"/>
+      <c r="AI12" t="inlineStr"/>
+      <c r="AJ12" t="inlineStr"/>
+      <c r="AK12" t="inlineStr"/>
+      <c r="AL12" t="inlineStr"/>
+      <c r="AM12" t="inlineStr"/>
+      <c r="AN12" t="inlineStr"/>
+      <c r="AO12" t="inlineStr"/>
+      <c r="AP12" t="inlineStr"/>
+      <c r="AQ12" t="inlineStr"/>
+      <c r="AR12" t="inlineStr"/>
+      <c r="AS12" t="inlineStr"/>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AU12" t="inlineStr"/>
+      <c r="AV12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr"/>
+      <c r="AX12" t="inlineStr"/>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr"/>
+      <c r="BA12" t="inlineStr"/>
+      <c r="BB12" t="inlineStr"/>
+      <c r="BC12" t="inlineStr"/>
+      <c r="BD12" t="inlineStr"/>
+      <c r="BE12" t="inlineStr"/>
+      <c r="BF12" t="inlineStr"/>
+      <c r="BG12" t="inlineStr"/>
+      <c r="BH12" t="inlineStr"/>
+      <c r="BI12" t="inlineStr"/>
+      <c r="BJ12" t="inlineStr"/>
+      <c r="BK12" t="inlineStr"/>
+      <c r="BL12" t="inlineStr"/>
+      <c r="BM12" t="inlineStr"/>
+      <c r="BN12" t="inlineStr"/>
+      <c r="BO12" t="inlineStr"/>
+      <c r="BP12" t="inlineStr"/>
+      <c r="BQ12" t="inlineStr"/>
+      <c r="BR12" t="inlineStr"/>
+      <c r="BS12" t="inlineStr"/>
+      <c r="BT12" t="inlineStr"/>
+      <c r="BU12" t="inlineStr"/>
+      <c r="BV12" t="inlineStr"/>
+      <c r="BW12" t="inlineStr"/>
+      <c r="BX12" t="inlineStr"/>
+      <c r="BY12" t="inlineStr"/>
+      <c r="BZ12" t="inlineStr"/>
+      <c r="CA12" t="inlineStr"/>
+      <c r="CB12" t="inlineStr"/>
+      <c r="CC12" t="inlineStr"/>
+      <c r="CD12" t="inlineStr"/>
+      <c r="CE12" t="inlineStr"/>
+      <c r="CF12" t="inlineStr"/>
+      <c r="CG12" t="inlineStr"/>
+      <c r="CH12" t="inlineStr"/>
+      <c r="CI12" t="inlineStr"/>
+      <c r="CJ12" t="inlineStr"/>
+      <c r="CK12" t="inlineStr"/>
+      <c r="CL12" t="inlineStr"/>
+      <c r="CM12" t="inlineStr"/>
+      <c r="CN12" t="inlineStr"/>
+      <c r="CO12" t="inlineStr"/>
+      <c r="CP12" t="inlineStr"/>
+      <c r="CQ12" t="inlineStr"/>
+      <c r="CR12" t="inlineStr"/>
+      <c r="CS12" t="inlineStr"/>
+      <c r="CT12" t="inlineStr"/>
+      <c r="CU12" t="inlineStr"/>
+      <c r="CV12" t="inlineStr"/>
+      <c r="CW12" t="inlineStr"/>
+      <c r="CX12" t="inlineStr"/>
+      <c r="CY12" t="inlineStr"/>
+      <c r="CZ12" t="inlineStr"/>
+      <c r="DA12" t="inlineStr"/>
+      <c r="DB12" t="inlineStr"/>
+      <c r="DC12" t="inlineStr"/>
+      <c r="DD12" t="inlineStr"/>
+      <c r="DE12" t="inlineStr"/>
+      <c r="DF12" t="inlineStr"/>
+      <c r="DG12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>pOGITkgl</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr"/>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr"/>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="M13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" t="inlineStr"/>
+      <c r="Q13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
+      <c r="AE13" t="inlineStr"/>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="inlineStr"/>
+      <c r="AH13" t="inlineStr"/>
+      <c r="AI13" t="inlineStr"/>
+      <c r="AJ13" t="inlineStr"/>
+      <c r="AK13" t="inlineStr"/>
+      <c r="AL13" t="inlineStr"/>
+      <c r="AM13" t="inlineStr"/>
+      <c r="AN13" t="inlineStr"/>
+      <c r="AO13" t="inlineStr"/>
+      <c r="AP13" t="inlineStr"/>
+      <c r="AQ13" t="inlineStr"/>
+      <c r="AR13" t="inlineStr"/>
+      <c r="AS13" t="inlineStr"/>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AU13" t="inlineStr"/>
+      <c r="AV13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr"/>
+      <c r="AX13" t="inlineStr"/>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr"/>
+      <c r="BA13" t="inlineStr"/>
+      <c r="BB13" t="inlineStr"/>
+      <c r="BC13" t="inlineStr"/>
+      <c r="BD13" t="inlineStr"/>
+      <c r="BE13" t="inlineStr"/>
+      <c r="BF13" t="inlineStr"/>
+      <c r="BG13" t="inlineStr"/>
+      <c r="BH13" t="inlineStr"/>
+      <c r="BI13" t="inlineStr"/>
+      <c r="BJ13" t="inlineStr"/>
+      <c r="BK13" t="inlineStr"/>
+      <c r="BL13" t="inlineStr"/>
+      <c r="BM13" t="inlineStr"/>
+      <c r="BN13" t="inlineStr"/>
+      <c r="BO13" t="inlineStr"/>
+      <c r="BP13" t="inlineStr"/>
+      <c r="BQ13" t="inlineStr"/>
+      <c r="BR13" t="inlineStr"/>
+      <c r="BS13" t="inlineStr"/>
+      <c r="BT13" t="inlineStr"/>
+      <c r="BU13" t="inlineStr"/>
+      <c r="BV13" t="inlineStr"/>
+      <c r="BW13" t="inlineStr"/>
+      <c r="BX13" t="inlineStr"/>
+      <c r="BY13" t="inlineStr"/>
+      <c r="BZ13" t="inlineStr"/>
+      <c r="CA13" t="inlineStr"/>
+      <c r="CB13" t="inlineStr"/>
+      <c r="CC13" t="inlineStr"/>
+      <c r="CD13" t="inlineStr"/>
+      <c r="CE13" t="inlineStr"/>
+      <c r="CF13" t="inlineStr"/>
+      <c r="CG13" t="inlineStr"/>
+      <c r="CH13" t="inlineStr"/>
+      <c r="CI13" t="inlineStr"/>
+      <c r="CJ13" t="inlineStr"/>
+      <c r="CK13" t="inlineStr"/>
+      <c r="CL13" t="inlineStr"/>
+      <c r="CM13" t="inlineStr"/>
+      <c r="CN13" t="inlineStr"/>
+      <c r="CO13" t="inlineStr"/>
+      <c r="CP13" t="inlineStr"/>
+      <c r="CQ13" t="inlineStr"/>
+      <c r="CR13" t="inlineStr"/>
+      <c r="CS13" t="inlineStr"/>
+      <c r="CT13" t="inlineStr"/>
+      <c r="CU13" t="inlineStr"/>
+      <c r="CV13" t="inlineStr"/>
+      <c r="CW13" t="inlineStr"/>
+      <c r="CX13" t="inlineStr"/>
+      <c r="CY13" t="inlineStr"/>
+      <c r="CZ13" t="inlineStr"/>
+      <c r="DA13" t="inlineStr"/>
+      <c r="DB13" t="inlineStr"/>
+      <c r="DC13" t="inlineStr"/>
+      <c r="DD13" t="inlineStr"/>
+      <c r="DE13" t="inlineStr"/>
+      <c r="DF13" t="inlineStr"/>
+      <c r="DG13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="inlineStr">
+        <is>
+          <t>E38ZP7hD</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr"/>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr"/>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr"/>
+      <c r="M14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" t="inlineStr"/>
+      <c r="Q14" t="inlineStr"/>
+      <c r="R14" t="inlineStr"/>
+      <c r="S14" t="inlineStr"/>
+      <c r="T14" t="inlineStr"/>
+      <c r="U14" t="inlineStr"/>
+      <c r="V14" t="inlineStr"/>
+      <c r="W14" t="inlineStr"/>
+      <c r="X14" t="inlineStr"/>
+      <c r="Y14" t="inlineStr"/>
+      <c r="Z14" t="inlineStr"/>
+      <c r="AA14" t="inlineStr"/>
+      <c r="AB14" t="inlineStr"/>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr"/>
+      <c r="AE14" t="inlineStr"/>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="inlineStr"/>
+      <c r="AH14" t="inlineStr"/>
+      <c r="AI14" t="inlineStr"/>
+      <c r="AJ14" t="inlineStr"/>
+      <c r="AK14" t="inlineStr"/>
+      <c r="AL14" t="inlineStr"/>
+      <c r="AM14" t="inlineStr"/>
+      <c r="AN14" t="inlineStr"/>
+      <c r="AO14" t="inlineStr"/>
+      <c r="AP14" t="inlineStr"/>
+      <c r="AQ14" t="inlineStr"/>
+      <c r="AR14" t="inlineStr"/>
+      <c r="AS14" t="inlineStr"/>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AU14" t="inlineStr"/>
+      <c r="AV14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr"/>
+      <c r="AX14" t="inlineStr"/>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr"/>
+      <c r="BA14" t="inlineStr"/>
+      <c r="BB14" t="inlineStr"/>
+      <c r="BC14" t="inlineStr"/>
+      <c r="BD14" t="inlineStr"/>
+      <c r="BE14" t="inlineStr"/>
+      <c r="BF14" t="inlineStr"/>
+      <c r="BG14" t="inlineStr"/>
+      <c r="BH14" t="inlineStr"/>
+      <c r="BI14" t="inlineStr"/>
+      <c r="BJ14" t="inlineStr"/>
+      <c r="BK14" t="inlineStr"/>
+      <c r="BL14" t="inlineStr"/>
+      <c r="BM14" t="inlineStr"/>
+      <c r="BN14" t="inlineStr"/>
+      <c r="BO14" t="inlineStr"/>
+      <c r="BP14" t="inlineStr"/>
+      <c r="BQ14" t="inlineStr"/>
+      <c r="BR14" t="inlineStr"/>
+      <c r="BS14" t="inlineStr"/>
+      <c r="BT14" t="inlineStr"/>
+      <c r="BU14" t="inlineStr"/>
+      <c r="BV14" t="inlineStr"/>
+      <c r="BW14" t="inlineStr"/>
+      <c r="BX14" t="inlineStr"/>
+      <c r="BY14" t="inlineStr"/>
+      <c r="BZ14" t="inlineStr"/>
+      <c r="CA14" t="inlineStr"/>
+      <c r="CB14" t="inlineStr"/>
+      <c r="CC14" t="inlineStr"/>
+      <c r="CD14" t="inlineStr"/>
+      <c r="CE14" t="inlineStr"/>
+      <c r="CF14" t="inlineStr"/>
+      <c r="CG14" t="inlineStr"/>
+      <c r="CH14" t="inlineStr"/>
+      <c r="CI14" t="inlineStr"/>
+      <c r="CJ14" t="inlineStr"/>
+      <c r="CK14" t="inlineStr"/>
+      <c r="CL14" t="inlineStr"/>
+      <c r="CM14" t="inlineStr"/>
+      <c r="CN14" t="inlineStr"/>
+      <c r="CO14" t="inlineStr"/>
+      <c r="CP14" t="inlineStr"/>
+      <c r="CQ14" t="inlineStr"/>
+      <c r="CR14" t="inlineStr"/>
+      <c r="CS14" t="inlineStr"/>
+      <c r="CT14" t="inlineStr"/>
+      <c r="CU14" t="inlineStr"/>
+      <c r="CV14" t="inlineStr"/>
+      <c r="CW14" t="inlineStr"/>
+      <c r="CX14" t="inlineStr"/>
+      <c r="CY14" t="inlineStr"/>
+      <c r="CZ14" t="inlineStr"/>
+      <c r="DA14" t="inlineStr"/>
+      <c r="DB14" t="inlineStr"/>
+      <c r="DC14" t="inlineStr"/>
+      <c r="DD14" t="inlineStr"/>
+      <c r="DE14" t="inlineStr"/>
+      <c r="DF14" t="inlineStr"/>
+      <c r="DG14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="inlineStr">
+        <is>
+          <t>fwAoyY0E</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr"/>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr"/>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" t="inlineStr"/>
+      <c r="Q15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr"/>
+      <c r="T15" t="inlineStr"/>
+      <c r="U15" t="inlineStr"/>
+      <c r="V15" t="inlineStr"/>
+      <c r="W15" t="inlineStr"/>
+      <c r="X15" t="inlineStr"/>
+      <c r="Y15" t="inlineStr"/>
+      <c r="Z15" t="inlineStr"/>
+      <c r="AA15" t="inlineStr"/>
+      <c r="AB15" t="inlineStr"/>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr"/>
+      <c r="AE15" t="inlineStr"/>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="inlineStr"/>
+      <c r="AH15" t="inlineStr"/>
+      <c r="AI15" t="inlineStr"/>
+      <c r="AJ15" t="inlineStr"/>
+      <c r="AK15" t="inlineStr"/>
+      <c r="AL15" t="inlineStr"/>
+      <c r="AM15" t="inlineStr"/>
+      <c r="AN15" t="inlineStr"/>
+      <c r="AO15" t="inlineStr"/>
+      <c r="AP15" t="inlineStr"/>
+      <c r="AQ15" t="inlineStr"/>
+      <c r="AR15" t="inlineStr"/>
+      <c r="AS15" t="inlineStr"/>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AU15" t="inlineStr"/>
+      <c r="AV15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr"/>
+      <c r="AX15" t="inlineStr"/>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr"/>
+      <c r="BA15" t="inlineStr"/>
+      <c r="BB15" t="inlineStr"/>
+      <c r="BC15" t="inlineStr"/>
+      <c r="BD15" t="inlineStr"/>
+      <c r="BE15" t="inlineStr"/>
+      <c r="BF15" t="inlineStr"/>
+      <c r="BG15" t="inlineStr"/>
+      <c r="BH15" t="inlineStr"/>
+      <c r="BI15" t="inlineStr"/>
+      <c r="BJ15" t="inlineStr"/>
+      <c r="BK15" t="inlineStr"/>
+      <c r="BL15" t="inlineStr"/>
+      <c r="BM15" t="inlineStr"/>
+      <c r="BN15" t="inlineStr"/>
+      <c r="BO15" t="inlineStr"/>
+      <c r="BP15" t="inlineStr"/>
+      <c r="BQ15" t="inlineStr"/>
+      <c r="BR15" t="inlineStr"/>
+      <c r="BS15" t="inlineStr"/>
+      <c r="BT15" t="inlineStr"/>
+      <c r="BU15" t="inlineStr"/>
+      <c r="BV15" t="inlineStr"/>
+      <c r="BW15" t="inlineStr"/>
+      <c r="BX15" t="inlineStr"/>
+      <c r="BY15" t="inlineStr"/>
+      <c r="BZ15" t="inlineStr"/>
+      <c r="CA15" t="inlineStr"/>
+      <c r="CB15" t="inlineStr"/>
+      <c r="CC15" t="inlineStr"/>
+      <c r="CD15" t="inlineStr"/>
+      <c r="CE15" t="inlineStr"/>
+      <c r="CF15" t="inlineStr"/>
+      <c r="CG15" t="inlineStr"/>
+      <c r="CH15" t="inlineStr"/>
+      <c r="CI15" t="inlineStr"/>
+      <c r="CJ15" t="inlineStr"/>
+      <c r="CK15" t="inlineStr"/>
+      <c r="CL15" t="inlineStr"/>
+      <c r="CM15" t="inlineStr"/>
+      <c r="CN15" t="inlineStr"/>
+      <c r="CO15" t="inlineStr"/>
+      <c r="CP15" t="inlineStr"/>
+      <c r="CQ15" t="inlineStr"/>
+      <c r="CR15" t="inlineStr"/>
+      <c r="CS15" t="inlineStr"/>
+      <c r="CT15" t="inlineStr"/>
+      <c r="CU15" t="inlineStr"/>
+      <c r="CV15" t="inlineStr"/>
+      <c r="CW15" t="inlineStr"/>
+      <c r="CX15" t="inlineStr"/>
+      <c r="CY15" t="inlineStr"/>
+      <c r="CZ15" t="inlineStr"/>
+      <c r="DA15" t="inlineStr"/>
+      <c r="DB15" t="inlineStr"/>
+      <c r="DC15" t="inlineStr"/>
+      <c r="DD15" t="inlineStr"/>
+      <c r="DE15" t="inlineStr"/>
+      <c r="DF15" t="inlineStr"/>
+      <c r="DG15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>SrjMmBpK</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr"/>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr"/>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" t="inlineStr"/>
+      <c r="Q16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr"/>
+      <c r="T16" t="inlineStr"/>
+      <c r="U16" t="inlineStr"/>
+      <c r="V16" t="inlineStr"/>
+      <c r="W16" t="inlineStr"/>
+      <c r="X16" t="inlineStr"/>
+      <c r="Y16" t="inlineStr"/>
+      <c r="Z16" t="inlineStr"/>
+      <c r="AA16" t="inlineStr"/>
+      <c r="AB16" t="inlineStr"/>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr"/>
+      <c r="AE16" t="inlineStr"/>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="inlineStr"/>
+      <c r="AH16" t="inlineStr"/>
+      <c r="AI16" t="inlineStr"/>
+      <c r="AJ16" t="inlineStr"/>
+      <c r="AK16" t="inlineStr"/>
+      <c r="AL16" t="inlineStr"/>
+      <c r="AM16" t="inlineStr"/>
+      <c r="AN16" t="inlineStr"/>
+      <c r="AO16" t="inlineStr"/>
+      <c r="AP16" t="inlineStr"/>
+      <c r="AQ16" t="inlineStr"/>
+      <c r="AR16" t="inlineStr"/>
+      <c r="AS16" t="inlineStr"/>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AU16" t="inlineStr"/>
+      <c r="AV16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr"/>
+      <c r="AX16" t="inlineStr"/>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr"/>
+      <c r="BA16" t="inlineStr"/>
+      <c r="BB16" t="inlineStr"/>
+      <c r="BC16" t="inlineStr"/>
+      <c r="BD16" t="inlineStr"/>
+      <c r="BE16" t="inlineStr"/>
+      <c r="BF16" t="inlineStr"/>
+      <c r="BG16" t="inlineStr"/>
+      <c r="BH16" t="inlineStr"/>
+      <c r="BI16" t="inlineStr"/>
+      <c r="BJ16" t="inlineStr"/>
+      <c r="BK16" t="inlineStr"/>
+      <c r="BL16" t="inlineStr"/>
+      <c r="BM16" t="inlineStr"/>
+      <c r="BN16" t="inlineStr"/>
+      <c r="BO16" t="inlineStr"/>
+      <c r="BP16" t="inlineStr"/>
+      <c r="BQ16" t="inlineStr"/>
+      <c r="BR16" t="inlineStr"/>
+      <c r="BS16" t="inlineStr"/>
+      <c r="BT16" t="inlineStr"/>
+      <c r="BU16" t="inlineStr"/>
+      <c r="BV16" t="inlineStr"/>
+      <c r="BW16" t="inlineStr"/>
+      <c r="BX16" t="inlineStr"/>
+      <c r="BY16" t="inlineStr"/>
+      <c r="BZ16" t="inlineStr"/>
+      <c r="CA16" t="inlineStr"/>
+      <c r="CB16" t="inlineStr"/>
+      <c r="CC16" t="inlineStr"/>
+      <c r="CD16" t="inlineStr"/>
+      <c r="CE16" t="inlineStr"/>
+      <c r="CF16" t="inlineStr"/>
+      <c r="CG16" t="inlineStr"/>
+      <c r="CH16" t="inlineStr"/>
+      <c r="CI16" t="inlineStr"/>
+      <c r="CJ16" t="inlineStr"/>
+      <c r="CK16" t="inlineStr"/>
+      <c r="CL16" t="inlineStr"/>
+      <c r="CM16" t="inlineStr"/>
+      <c r="CN16" t="inlineStr"/>
+      <c r="CO16" t="inlineStr"/>
+      <c r="CP16" t="inlineStr"/>
+      <c r="CQ16" t="inlineStr"/>
+      <c r="CR16" t="inlineStr"/>
+      <c r="CS16" t="inlineStr"/>
+      <c r="CT16" t="inlineStr"/>
+      <c r="CU16" t="inlineStr"/>
+      <c r="CV16" t="inlineStr"/>
+      <c r="CW16" t="inlineStr"/>
+      <c r="CX16" t="inlineStr"/>
+      <c r="CY16" t="inlineStr"/>
+      <c r="CZ16" t="inlineStr"/>
+      <c r="DA16" t="inlineStr"/>
+      <c r="DB16" t="inlineStr"/>
+      <c r="DC16" t="inlineStr"/>
+      <c r="DD16" t="inlineStr"/>
+      <c r="DE16" t="inlineStr"/>
+      <c r="DF16" t="inlineStr"/>
+      <c r="DG16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="inlineStr">
+        <is>
+          <t>6w5RRTN0</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr"/>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr"/>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" t="inlineStr"/>
+      <c r="Q17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr"/>
+      <c r="T17" t="inlineStr"/>
+      <c r="U17" t="inlineStr"/>
+      <c r="V17" t="inlineStr"/>
+      <c r="W17" t="inlineStr"/>
+      <c r="X17" t="inlineStr"/>
+      <c r="Y17" t="inlineStr"/>
+      <c r="Z17" t="inlineStr"/>
+      <c r="AA17" t="inlineStr"/>
+      <c r="AB17" t="inlineStr"/>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr"/>
+      <c r="AE17" t="inlineStr"/>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="inlineStr"/>
+      <c r="AH17" t="inlineStr"/>
+      <c r="AI17" t="inlineStr"/>
+      <c r="AJ17" t="inlineStr"/>
+      <c r="AK17" t="inlineStr"/>
+      <c r="AL17" t="inlineStr"/>
+      <c r="AM17" t="inlineStr"/>
+      <c r="AN17" t="inlineStr"/>
+      <c r="AO17" t="inlineStr"/>
+      <c r="AP17" t="inlineStr"/>
+      <c r="AQ17" t="inlineStr"/>
+      <c r="AR17" t="inlineStr"/>
+      <c r="AS17" t="inlineStr"/>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AU17" t="inlineStr"/>
+      <c r="AV17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr"/>
+      <c r="AX17" t="inlineStr"/>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr"/>
+      <c r="BA17" t="inlineStr"/>
+      <c r="BB17" t="inlineStr"/>
+      <c r="BC17" t="inlineStr"/>
+      <c r="BD17" t="inlineStr"/>
+      <c r="BE17" t="inlineStr"/>
+      <c r="BF17" t="inlineStr"/>
+      <c r="BG17" t="inlineStr"/>
+      <c r="BH17" t="inlineStr"/>
+      <c r="BI17" t="inlineStr"/>
+      <c r="BJ17" t="inlineStr"/>
+      <c r="BK17" t="inlineStr"/>
+      <c r="BL17" t="inlineStr"/>
+      <c r="BM17" t="inlineStr"/>
+      <c r="BN17" t="inlineStr"/>
+      <c r="BO17" t="inlineStr"/>
+      <c r="BP17" t="inlineStr"/>
+      <c r="BQ17" t="inlineStr"/>
+      <c r="BR17" t="inlineStr"/>
+      <c r="BS17" t="inlineStr"/>
+      <c r="BT17" t="inlineStr"/>
+      <c r="BU17" t="inlineStr"/>
+      <c r="BV17" t="inlineStr"/>
+      <c r="BW17" t="inlineStr"/>
+      <c r="BX17" t="inlineStr"/>
+      <c r="BY17" t="inlineStr"/>
+      <c r="BZ17" t="inlineStr"/>
+      <c r="CA17" t="inlineStr"/>
+      <c r="CB17" t="inlineStr"/>
+      <c r="CC17" t="inlineStr"/>
+      <c r="CD17" t="inlineStr"/>
+      <c r="CE17" t="inlineStr"/>
+      <c r="CF17" t="inlineStr"/>
+      <c r="CG17" t="inlineStr"/>
+      <c r="CH17" t="inlineStr"/>
+      <c r="CI17" t="inlineStr"/>
+      <c r="CJ17" t="inlineStr"/>
+      <c r="CK17" t="inlineStr"/>
+      <c r="CL17" t="inlineStr"/>
+      <c r="CM17" t="inlineStr"/>
+      <c r="CN17" t="inlineStr"/>
+      <c r="CO17" t="inlineStr"/>
+      <c r="CP17" t="inlineStr"/>
+      <c r="CQ17" t="inlineStr"/>
+      <c r="CR17" t="inlineStr"/>
+      <c r="CS17" t="inlineStr"/>
+      <c r="CT17" t="inlineStr"/>
+      <c r="CU17" t="inlineStr"/>
+      <c r="CV17" t="inlineStr"/>
+      <c r="CW17" t="inlineStr"/>
+      <c r="CX17" t="inlineStr"/>
+      <c r="CY17" t="inlineStr"/>
+      <c r="CZ17" t="inlineStr"/>
+      <c r="DA17" t="inlineStr"/>
+      <c r="DB17" t="inlineStr"/>
+      <c r="DC17" t="inlineStr"/>
+      <c r="DD17" t="inlineStr"/>
+      <c r="DE17" t="inlineStr"/>
+      <c r="DF17" t="inlineStr"/>
+      <c r="DG17" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
